--- a/04_Figures/F06_prediction/modules/trajectory/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/trajectory/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -143,88 +143,58 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_yellow@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_pink@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_blue@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_green@T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_red@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_blue@T3</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_brown@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_green@T2</t>
+    <t xml:space="preserve">ME_black@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple@T3</t>
+    <t xml:space="preserve">ME_greenyellow@T3</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_red@T3</t>
+    <t xml:space="preserve">ME_black@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan@T3</t>
+    <t xml:space="preserve">ME_black@T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_blue@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_green@T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_greenyellow@T2</t>
   </si>
   <si>
     <t xml:space="preserve">ME_magenta@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_magenta@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_blue@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_red@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_pink@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_blue@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow@T2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_pink@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_purple@T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_greenyellow@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_red@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_greenyellow@T2</t>
   </si>
   <si>
     <t xml:space="preserve">ME_purple@T1</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_black@T1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_magenta@T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_yellow@T3</t>
+    <t xml:space="preserve">ME_pink@T2</t>
   </si>
 </sst>
 </file>
@@ -611,16 +581,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.363579652066767</v>
+        <v>-0.591901940112975</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.947252747252747</v>
+        <v>-0.907692307692308</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -644,28 +614,28 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.363579652066767</v>
+        <v>-0.591901940112975</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.947252747252747</v>
+        <v>-0.907692307692308</v>
       </c>
       <c r="J3" t="n">
-        <v>0.751243781094527</v>
+        <v>0.900497512437811</v>
       </c>
       <c r="K3" t="n">
-        <v>0.447761194029851</v>
+        <v>0.407960199004975</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.250979081944951</v>
+        <v>-0.25244872666787</v>
       </c>
       <c r="M3" t="n">
-        <v>0.236837020255251</v>
+        <v>0.341298677167112</v>
       </c>
     </row>
     <row r="4">
@@ -685,16 +655,16 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0442701205315816</v>
+        <v>-0.159763313609468</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="J4"/>
       <c r="K4"/>
@@ -718,28 +688,28 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0442701205315816</v>
+        <v>-0.159763313609468</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0646766169154229</v>
+        <v>0.393034825870647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.129353233830846</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.27638924277598</v>
+        <v>-0.318416837358057</v>
       </c>
       <c r="M5" t="n">
-        <v>0.243426355842675</v>
+        <v>0.343495405318035</v>
       </c>
     </row>
     <row r="6">
@@ -759,16 +729,16 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.408178933279013</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.934065934065934</v>
+        <v>-1</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -792,28 +762,28 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.408178933279013</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.934065934065934</v>
+        <v>-1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.880597014925373</v>
+        <v>0.298507462686567</v>
       </c>
       <c r="K7" t="n">
-        <v>0.348258706467662</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.253906503075626</v>
+        <v>-0.27388103557954</v>
       </c>
       <c r="M7" t="n">
-        <v>0.255476439025247</v>
+        <v>0.27181014548928</v>
       </c>
     </row>
     <row r="8">
@@ -833,16 +803,16 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.403568158206214</v>
+        <v>0.282583392968293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.463736263736264</v>
       </c>
       <c r="J8"/>
       <c r="K8"/>
@@ -866,28 +836,28 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>0.403568158206214</v>
+        <v>0.282583392968293</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>0.463736263736264</v>
       </c>
       <c r="J9" t="n">
         <v>0.0149253731343284</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0199004975124378</v>
+        <v>0.0149253731343284</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.241974808004407</v>
+        <v>-0.231537184185335</v>
       </c>
       <c r="M9" t="n">
-        <v>0.237223466744276</v>
+        <v>0.215716391897721</v>
       </c>
     </row>
     <row r="10">
@@ -907,16 +877,16 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.190457293075894</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.996690559042565</v>
+        <v>-0.987850731467909</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -940,28 +910,28 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.190457293075894</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.996690559042565</v>
+        <v>-0.987850731467909</v>
       </c>
       <c r="J11" t="n">
-        <v>0.388059701492537</v>
+        <v>0.442786069651741</v>
       </c>
       <c r="K11" t="n">
-        <v>0.805970149253731</v>
+        <v>0.63681592039801</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.305911722354123</v>
+        <v>-0.287501619286255</v>
       </c>
       <c r="M11" t="n">
-        <v>0.266618465949945</v>
+        <v>0.279596156555038</v>
       </c>
     </row>
     <row r="12">
@@ -981,7 +951,7 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1014,7 +984,7 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
@@ -1032,10 +1002,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.321987599238094</v>
+        <v>-0.346895025747231</v>
       </c>
       <c r="M13" t="n">
-        <v>0.25823651726702</v>
+        <v>0.273729925235617</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1038,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.407384698106139</v>
       </c>
     </row>
     <row r="3">
@@ -1090,7 +1060,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0241824704458287</v>
+        <v>-0.369766433609751</v>
       </c>
     </row>
     <row r="5">
@@ -1101,7 +1071,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.217194745067228</v>
+        <v>-0.19002915486318</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1082,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.344501169949937</v>
+        <v>-0.397620824965034</v>
       </c>
     </row>
     <row r="7">
@@ -1123,7 +1093,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.90299541503975</v>
+        <v>-1.31581231849856</v>
       </c>
     </row>
     <row r="8">
@@ -1134,7 +1104,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.745774965782492</v>
+        <v>-0.474427684399281</v>
       </c>
     </row>
     <row r="9">
@@ -1145,7 +1115,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.345195714788366</v>
+        <v>-0.353735646556452</v>
       </c>
     </row>
     <row r="10">
@@ -1167,7 +1137,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.162849662713996</v>
+        <v>-0.19983942701193</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1148,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.253900522304091</v>
       </c>
     </row>
     <row r="13">
@@ -1189,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.209630904127722</v>
+        <v>-0.358216717327508</v>
       </c>
     </row>
     <row r="14">
@@ -1222,7 +1192,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.285782496946247</v>
+        <v>-0.325049781854251</v>
       </c>
     </row>
     <row r="17">
@@ -1233,7 +1203,7 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.371328636816761</v>
+        <v>-0.298873996338959</v>
       </c>
     </row>
     <row r="18">
@@ -1244,7 +1214,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.596958944490976</v>
+        <v>-0.190127630442419</v>
       </c>
     </row>
     <row r="19">
@@ -1255,7 +1225,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.246948889332989</v>
+        <v>-0.147154222058891</v>
       </c>
     </row>
     <row r="20">
@@ -1266,7 +1236,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.311829300449496</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="21">
@@ -1288,7 +1258,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0426258201770733</v>
+        <v>-0.23593727636821</v>
       </c>
     </row>
     <row r="23">
@@ -1310,7 +1280,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.328101133854852</v>
       </c>
     </row>
     <row r="25">
@@ -1332,7 +1302,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.100914412505979</v>
+        <v>-0.201096570654804</v>
       </c>
     </row>
     <row r="27">
@@ -1343,7 +1313,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.824952831846835</v>
+        <v>-0.40645322449525</v>
       </c>
     </row>
     <row r="28">
@@ -1354,7 +1324,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.543814645968791</v>
+        <v>-0.618208261536348</v>
       </c>
     </row>
     <row r="29">
@@ -1365,7 +1335,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.133546263676764</v>
+        <v>-0.0232469142025944</v>
       </c>
     </row>
     <row r="30">
@@ -1376,7 +1346,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.59874567579213</v>
       </c>
     </row>
     <row r="31">
@@ -1398,7 +1368,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.626330630759226</v>
+        <v>-0.646242047482012</v>
       </c>
     </row>
     <row r="33">
@@ -1420,7 +1390,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.32177888196598</v>
+        <v>-0.387480083764131</v>
       </c>
     </row>
     <row r="35">
@@ -1431,7 +1401,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.336741325482644</v>
+        <v>-0.326877416715827</v>
       </c>
     </row>
     <row r="36">
@@ -1442,7 +1412,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.383541472960021</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="37">
@@ -1464,7 +1434,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.289830226937347</v>
+        <v>-0.267988798043676</v>
       </c>
     </row>
     <row r="39">
@@ -1475,7 +1445,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.176277049470888</v>
+        <v>-0.209898910627703</v>
       </c>
     </row>
     <row r="40">
@@ -1486,7 +1456,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.317667851972516</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="41">
@@ -1497,7 +1467,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.176016552885703</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="42">
@@ -1541,7 +1511,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.160313988700999</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="46">
@@ -1552,7 +1522,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.589685167533332</v>
+        <v>-0.16113772594879</v>
       </c>
     </row>
     <row r="47">
@@ -1574,7 +1544,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.161152197225895</v>
+        <v>-0.253425236460122</v>
       </c>
     </row>
     <row r="49">
@@ -1585,7 +1555,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.400002942081163</v>
+        <v>-0.042680493662492</v>
       </c>
     </row>
     <row r="50">
@@ -1596,7 +1566,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.209769679483052</v>
+        <v>-0.213013828181514</v>
       </c>
     </row>
     <row r="51">
@@ -1607,7 +1577,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.636654805763776</v>
+        <v>-0.460477639937154</v>
       </c>
     </row>
     <row r="52">
@@ -1618,7 +1588,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.392660947424136</v>
+        <v>-0.222485982062723</v>
       </c>
     </row>
     <row r="53">
@@ -1629,7 +1599,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.259039095159044</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="54">
@@ -1651,7 +1621,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.347779440295626</v>
+        <v>-0.262456273090569</v>
       </c>
     </row>
     <row r="56">
@@ -1662,7 +1632,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.086487511499485</v>
+        <v>0.325869755609381</v>
       </c>
     </row>
     <row r="57">
@@ -1673,7 +1643,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.230757364615142</v>
+        <v>-0.265971003587896</v>
       </c>
     </row>
     <row r="58">
@@ -1695,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>0.106451782418282</v>
+        <v>0.334334478649289</v>
       </c>
     </row>
     <row r="60">
@@ -1717,7 +1687,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>0.441873061805861</v>
+        <v>0.264369978421156</v>
       </c>
     </row>
     <row r="62">
@@ -1739,7 +1709,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.17934631257169</v>
+        <v>-0.272607460833657</v>
       </c>
     </row>
     <row r="64">
@@ -1750,7 +1720,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.25702314839506</v>
+        <v>-0.339684084511044</v>
       </c>
     </row>
     <row r="65">
@@ -1761,7 +1731,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.24080316517065</v>
+        <v>-0.209316130044277</v>
       </c>
     </row>
     <row r="66">
@@ -1772,7 +1742,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.398805586789445</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="67">
@@ -1783,7 +1753,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.230191407756646</v>
       </c>
     </row>
     <row r="68">
@@ -1805,7 +1775,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.401370403764414</v>
+        <v>-0.203281281941372</v>
       </c>
     </row>
     <row r="70">
@@ -1816,7 +1786,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.438990612911453</v>
       </c>
     </row>
     <row r="71">
@@ -1827,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.565643104875533</v>
+        <v>-0.632602694271818</v>
       </c>
     </row>
     <row r="72">
@@ -1849,7 +1819,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.202479754262365</v>
+        <v>-0.224507522044658</v>
       </c>
     </row>
     <row r="74">
@@ -1860,7 +1830,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.597640669184388</v>
+        <v>-0.592142717931136</v>
       </c>
     </row>
     <row r="75">
@@ -1871,7 +1841,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.221106393918928</v>
+        <v>-0.400235289770795</v>
       </c>
     </row>
     <row r="76">
@@ -1904,7 +1874,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.224114890966341</v>
+        <v>-0.194118050315022</v>
       </c>
     </row>
     <row r="79">
@@ -1915,7 +1885,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.455025202062558</v>
+        <v>-0.476705156661482</v>
       </c>
     </row>
     <row r="80">
@@ -1926,7 +1896,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.255527270673699</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="81">
@@ -1937,7 +1907,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.394434352758955</v>
+        <v>-0.375842010015712</v>
       </c>
     </row>
     <row r="82">
@@ -1948,7 +1918,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.285853934685547</v>
+        <v>-0.253513182616747</v>
       </c>
     </row>
     <row r="83">
@@ -1981,7 +1951,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00235938222241217</v>
+        <v>-0.324143503479487</v>
       </c>
     </row>
     <row r="86">
@@ -1992,7 +1962,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>0.584497151097159</v>
+        <v>0.035990511154023</v>
       </c>
     </row>
     <row r="87">
@@ -2014,7 +1984,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.304790156112243</v>
+        <v>-0.252904326080621</v>
       </c>
     </row>
     <row r="89">
@@ -2025,7 +1995,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.375915105652186</v>
+        <v>0.333501200277797</v>
       </c>
     </row>
     <row r="90">
@@ -2036,7 +2006,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.33202507725908</v>
+        <v>-0.105893056158587</v>
       </c>
     </row>
     <row r="91">
@@ -2058,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.408190472296626</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="93">
@@ -2069,7 +2039,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.346078291161556</v>
+        <v>0.118007443678832</v>
       </c>
     </row>
     <row r="94">
@@ -2080,7 +2050,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.143616564795233</v>
+        <v>-0.0167897954380403</v>
       </c>
     </row>
     <row r="95">
@@ -2102,7 +2072,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.251946744018735</v>
       </c>
     </row>
     <row r="97">
@@ -2113,7 +2083,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.685639010748813</v>
       </c>
     </row>
     <row r="98">
@@ -2124,7 +2094,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.618655940920278</v>
+        <v>-0.424103087000248</v>
       </c>
     </row>
     <row r="99">
@@ -2135,7 +2105,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.219032253972817</v>
+        <v>-0.197842926274749</v>
       </c>
     </row>
     <row r="100">
@@ -2157,7 +2127,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.150697922286944</v>
+        <v>0.0708343583163901</v>
       </c>
     </row>
     <row r="102">
@@ -2168,7 +2138,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.435793215331443</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="103">
@@ -2179,7 +2149,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.186367809493215</v>
+        <v>-0.30429006862982</v>
       </c>
     </row>
     <row r="104">
@@ -2190,7 +2160,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.493340742230921</v>
+        <v>-0.464971193481818</v>
       </c>
     </row>
     <row r="105">
@@ -2201,7 +2171,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.054209669624196</v>
+        <v>-0.0198879338066074</v>
       </c>
     </row>
     <row r="106">
@@ -2234,7 +2204,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0177952344519574</v>
       </c>
     </row>
     <row r="109">
@@ -2245,7 +2215,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.27252128935293</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="110">
@@ -2256,7 +2226,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.173575831580042</v>
+        <v>-0.0911987899759463</v>
       </c>
     </row>
     <row r="111">
@@ -2267,7 +2237,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.622035459432784</v>
       </c>
     </row>
     <row r="112">
@@ -2278,7 +2248,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.451062588364104</v>
+        <v>-0.193682663901986</v>
       </c>
     </row>
     <row r="113">
@@ -2289,7 +2259,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.480725590205899</v>
+        <v>-0.332319700056883</v>
       </c>
     </row>
     <row r="114">
@@ -2300,7 +2270,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.315496244046784</v>
+        <v>-0.255299487000194</v>
       </c>
     </row>
     <row r="115">
@@ -2311,7 +2281,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>0.379092199384101</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="116">
@@ -2322,7 +2292,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.1910298575607</v>
+        <v>-0.340426156946476</v>
       </c>
     </row>
     <row r="117">
@@ -2333,7 +2303,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.178495836700229</v>
+        <v>-0.166059153485964</v>
       </c>
     </row>
     <row r="118">
@@ -2344,7 +2314,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.564122203866465</v>
+        <v>-0.307850354151827</v>
       </c>
     </row>
     <row r="119">
@@ -2355,7 +2325,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.181080995157595</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="120">
@@ -2366,7 +2336,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.245763809290896</v>
+        <v>-0.489309792705483</v>
       </c>
     </row>
     <row r="121">
@@ -2377,7 +2347,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.358583880070675</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="122">
@@ -2388,7 +2358,7 @@
         <v>16</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.458073895603559</v>
+        <v>-0.348121394477567</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2369,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>0.137609085242931</v>
+        <v>0.291922898238808</v>
       </c>
     </row>
     <row r="124">
@@ -2410,7 +2380,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.230522486216362</v>
+        <v>0.0738031834900047</v>
       </c>
     </row>
     <row r="125">
@@ -2443,7 +2413,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.163346165947839</v>
+        <v>-0.916463439796033</v>
       </c>
     </row>
     <row r="128">
@@ -2454,7 +2424,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.178182571844218</v>
+        <v>-0.187113764223576</v>
       </c>
     </row>
     <row r="129">
@@ -2476,7 +2446,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.176518940071675</v>
+        <v>-0.208452553846864</v>
       </c>
     </row>
     <row r="131">
@@ -2487,7 +2457,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.576722607846947</v>
+        <v>-0.493968572202087</v>
       </c>
     </row>
     <row r="132">
@@ -2498,7 +2468,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.279586438840866</v>
+        <v>-0.251800438192096</v>
       </c>
     </row>
     <row r="133">
@@ -2531,7 +2501,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.572521201055876</v>
+        <v>-0.384930319774136</v>
       </c>
     </row>
     <row r="136">
@@ -2575,7 +2545,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.50519070131314</v>
+        <v>-0.489154417158123</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2556,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.529453437718508</v>
+        <v>-0.544679788281243</v>
       </c>
     </row>
     <row r="141">
@@ -2597,7 +2567,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.0853629496508821</v>
+        <v>0.0645390073646799</v>
       </c>
     </row>
     <row r="142">
@@ -2608,7 +2578,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>0.41381289878874</v>
+        <v>0.148429521766774</v>
       </c>
     </row>
     <row r="143">
@@ -2630,7 +2600,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.172423711029016</v>
+        <v>-0.175185307833895</v>
       </c>
     </row>
     <row r="145">
@@ -2641,7 +2611,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.233518484079579</v>
+        <v>-0.147127477444163</v>
       </c>
     </row>
     <row r="146">
@@ -2652,7 +2622,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.372634454114441</v>
+        <v>0.162693231232866</v>
       </c>
     </row>
     <row r="147">
@@ -2674,7 +2644,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.32255443877527</v>
+        <v>-0.43257091217698</v>
       </c>
     </row>
     <row r="149">
@@ -2696,7 +2666,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.107585630460996</v>
+        <v>0.520023571902481</v>
       </c>
     </row>
     <row r="151">
@@ -2718,7 +2688,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.271696311038274</v>
+        <v>-0.0300156006099901</v>
       </c>
     </row>
     <row r="153">
@@ -2729,7 +2699,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>0.106920327368096</v>
+        <v>0.50426144470898</v>
       </c>
     </row>
     <row r="154">
@@ -2740,7 +2710,7 @@
         <v>16</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.508609061541067</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="155">
@@ -2751,7 +2721,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.74536675640523</v>
+        <v>-2.74662913109571</v>
       </c>
     </row>
     <row r="156">
@@ -2762,7 +2732,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.98657983992952</v>
+        <v>-0.848316073675296</v>
       </c>
     </row>
     <row r="157">
@@ -2773,7 +2743,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.391365060480521</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="158">
@@ -2784,7 +2754,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-1.00336651337764</v>
+        <v>-1.00582278496287</v>
       </c>
     </row>
     <row r="159">
@@ -2795,7 +2765,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.173675968465114</v>
+        <v>-0.170958143186756</v>
       </c>
     </row>
     <row r="160">
@@ -2806,7 +2776,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>0.277956792006005</v>
+        <v>0.456667480776354</v>
       </c>
     </row>
     <row r="161">
@@ -2817,7 +2787,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.216545013813426</v>
       </c>
     </row>
     <row r="162">
@@ -2828,7 +2798,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.329650552976868</v>
+        <v>-1.45117489310442</v>
       </c>
     </row>
     <row r="163">
@@ -2839,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.156362267538886</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="164">
@@ -2850,7 +2820,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.165923070140616</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="165">
@@ -2861,7 +2831,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.279702373661829</v>
+        <v>-0.313551683255769</v>
       </c>
     </row>
     <row r="166">
@@ -2872,7 +2842,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.436179036155971</v>
+        <v>-1.94172534914808</v>
       </c>
     </row>
     <row r="167">
@@ -2883,7 +2853,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.117348296891391</v>
+        <v>-0.323033252940864</v>
       </c>
     </row>
     <row r="168">
@@ -2894,7 +2864,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.126803326460406</v>
+        <v>0.24889559537122</v>
       </c>
     </row>
     <row r="169">
@@ -2905,7 +2875,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.139274996340244</v>
+        <v>-0.243531428919403</v>
       </c>
     </row>
     <row r="170">
@@ -2916,7 +2886,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.472292363519835</v>
+        <v>-0.22830034487679</v>
       </c>
     </row>
     <row r="171">
@@ -2927,7 +2897,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.251589617789246</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="172">
@@ -2938,7 +2908,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.356205887232589</v>
+        <v>-0.62637053514844</v>
       </c>
     </row>
     <row r="173">
@@ -2949,7 +2919,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.384651516642692</v>
+        <v>-0.443796148227056</v>
       </c>
     </row>
     <row r="174">
@@ -2960,7 +2930,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.342575250796066</v>
+        <v>-0.298517756727558</v>
       </c>
     </row>
     <row r="175">
@@ -2971,7 +2941,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.262764701228698</v>
+        <v>-0.115646041810809</v>
       </c>
     </row>
     <row r="176">
@@ -2982,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.069500308202616</v>
+        <v>-0.00813057527986194</v>
       </c>
     </row>
     <row r="177">
@@ -2993,7 +2963,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.351144468799832</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="178">
@@ -3004,7 +2974,7 @@
         <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.37025196850491</v>
+        <v>-1.05456325767962</v>
       </c>
     </row>
     <row r="179">
@@ -3015,7 +2985,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.414525062055555</v>
+        <v>-0.430810820306521</v>
       </c>
     </row>
     <row r="180">
@@ -3026,7 +2996,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.222335297777221</v>
+        <v>-0.233212246521353</v>
       </c>
     </row>
     <row r="181">
@@ -3037,7 +3007,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.387160221322079</v>
+        <v>-0.432620597046645</v>
       </c>
     </row>
     <row r="182">
@@ -3048,7 +3018,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.447952055609492</v>
+        <v>-0.31562828480226</v>
       </c>
     </row>
     <row r="183">
@@ -3070,7 +3040,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.499980302609966</v>
+        <v>-0.77666355537562</v>
       </c>
     </row>
     <row r="185">
@@ -3081,7 +3051,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.397284995366312</v>
+        <v>-0.0136759865990905</v>
       </c>
     </row>
     <row r="186">
@@ -3092,7 +3062,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.242031223566531</v>
+        <v>-0.238585918728143</v>
       </c>
     </row>
     <row r="187">
@@ -3125,7 +3095,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>0.415407756472264</v>
+        <v>0.558727123706542</v>
       </c>
     </row>
     <row r="190">
@@ -3136,7 +3106,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>0.512796033239447</v>
+        <v>0.119154608055183</v>
       </c>
     </row>
     <row r="191">
@@ -3147,7 +3117,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.267406137931105</v>
+        <v>-0.294537803124969</v>
       </c>
     </row>
     <row r="192">
@@ -3158,7 +3128,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.33658835996302</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="193">
@@ -3180,7 +3150,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.12740472920208</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="195">
@@ -3191,7 +3161,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.143967687788219</v>
+        <v>-0.191097876906904</v>
       </c>
     </row>
     <row r="196">
@@ -3213,7 +3183,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.437628732829745</v>
+        <v>-0.38452103521296</v>
       </c>
     </row>
     <row r="198">
@@ -3224,7 +3194,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.233523017475782</v>
+        <v>0.108759310025965</v>
       </c>
     </row>
     <row r="199">
@@ -3235,7 +3205,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.30755010614995</v>
+        <v>-0.61261871957806</v>
       </c>
     </row>
     <row r="200">
@@ -3246,7 +3216,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.471536827338029</v>
+        <v>-0.903086891926463</v>
       </c>
     </row>
     <row r="201">
@@ -3257,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>-0.618795501056563</v>
+        <v>-0.647206136514807</v>
       </c>
     </row>
     <row r="202">
@@ -3279,7 +3249,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.169071546581747</v>
+        <v>-0.221566580912778</v>
       </c>
     </row>
     <row r="204">
@@ -3290,7 +3260,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.205905786324835</v>
+        <v>-0.269348843849681</v>
       </c>
     </row>
     <row r="205">
@@ -3312,7 +3282,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.515981127180044</v>
+        <v>-0.440456379758755</v>
       </c>
     </row>
     <row r="207">
@@ -3323,7 +3293,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.470620223920036</v>
+        <v>-2.16626003407773</v>
       </c>
     </row>
     <row r="208">
@@ -3334,7 +3304,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.238608173010289</v>
+        <v>-0.228311474482763</v>
       </c>
     </row>
     <row r="209">
@@ -3345,7 +3315,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.16845372151745</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="210">
@@ -3356,7 +3326,7 @@
         <v>16</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.197243797489988</v>
+        <v>-0.206792078955536</v>
       </c>
     </row>
     <row r="211">
@@ -3367,7 +3337,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.214319886663084</v>
+        <v>-0.215315517848975</v>
       </c>
     </row>
     <row r="212">
@@ -3378,7 +3348,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.377923678081449</v>
+        <v>-0.517963195321547</v>
       </c>
     </row>
     <row r="213">
@@ -3389,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.181563328057476</v>
+        <v>-0.152217509513403</v>
       </c>
     </row>
     <row r="214">
@@ -3411,7 +3381,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.191031955983831</v>
+        <v>-0.24993515437501</v>
       </c>
     </row>
     <row r="216">
@@ -3422,7 +3392,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.3827454971609</v>
+        <v>-0.242236250852408</v>
       </c>
     </row>
     <row r="217">
@@ -3433,7 +3403,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>0.12897090260799</v>
+        <v>-0.0600184853797165</v>
       </c>
     </row>
     <row r="218">
@@ -3444,7 +3414,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.352326243267638</v>
+        <v>-0.34838682883239</v>
       </c>
     </row>
     <row r="219">
@@ -3455,7 +3425,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.379277355848027</v>
+        <v>-0.470618916558564</v>
       </c>
     </row>
     <row r="220">
@@ -3488,7 +3458,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.325754502624716</v>
+        <v>0.0234198782726717</v>
       </c>
     </row>
     <row r="223">
@@ -3510,7 +3480,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.310035481096187</v>
       </c>
     </row>
     <row r="225">
@@ -3521,7 +3491,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.208166745812423</v>
+        <v>-0.25536442328932</v>
       </c>
     </row>
     <row r="226">
@@ -3532,7 +3502,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>0.295555405488694</v>
+        <v>0.0608550035925879</v>
       </c>
     </row>
     <row r="227">
@@ -3543,7 +3513,7 @@
         <v>16</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.778986093227539</v>
+        <v>-0.327374518090218</v>
       </c>
     </row>
     <row r="228">
@@ -3554,7 +3524,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.116700390195069</v>
+        <v>-0.325318582776478</v>
       </c>
     </row>
     <row r="229">
@@ -3565,7 +3535,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.623750530992913</v>
+        <v>-0.578369073728864</v>
       </c>
     </row>
     <row r="230">
@@ -3576,7 +3546,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.946673372211495</v>
+        <v>-0.647699195222819</v>
       </c>
     </row>
     <row r="231">
@@ -3587,7 +3557,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.443366359268641</v>
+        <v>-0.631429542822928</v>
       </c>
     </row>
     <row r="232">
@@ -3598,7 +3568,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.455715248947148</v>
+        <v>-0.643776507949117</v>
       </c>
     </row>
     <row r="233">
@@ -3609,7 +3579,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.279340473648881</v>
       </c>
     </row>
     <row r="234">
@@ -3631,7 +3601,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>0.518187914145465</v>
+        <v>0.613995835829084</v>
       </c>
     </row>
     <row r="236">
@@ -3642,7 +3612,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.564942498381422</v>
+        <v>-1.24704593687373</v>
       </c>
     </row>
     <row r="237">
@@ -3653,7 +3623,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.365999927048297</v>
+        <v>-0.248096669394388</v>
       </c>
     </row>
     <row r="238">
@@ -3664,7 +3634,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.237694080664234</v>
+        <v>-0.446169322826407</v>
       </c>
     </row>
     <row r="239">
@@ -3675,7 +3645,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.529372104054872</v>
+        <v>0.0418746252590991</v>
       </c>
     </row>
     <row r="240">
@@ -3686,7 +3656,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.185431775779862</v>
+        <v>-0.176253746239912</v>
       </c>
     </row>
     <row r="241">
@@ -3697,7 +3667,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-0.214372068495224</v>
+        <v>-1.4278696554168</v>
       </c>
     </row>
     <row r="242">
@@ -3730,7 +3700,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-0.344994994168936</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="245">
@@ -3741,7 +3711,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.158784327924542</v>
+        <v>-0.129729273969998</v>
       </c>
     </row>
     <row r="246">
@@ -3752,7 +3722,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.985019238610028</v>
+        <v>-0.411983408128407</v>
       </c>
     </row>
     <row r="247">
@@ -3763,7 +3733,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.15774543686166</v>
+        <v>-0.511137848145617</v>
       </c>
     </row>
     <row r="248">
@@ -3774,7 +3744,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.174145925295812</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="249">
@@ -3785,7 +3755,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.471057877128506</v>
+        <v>-0.568311183611153</v>
       </c>
     </row>
     <row r="250">
@@ -3807,7 +3777,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.135041744278211</v>
+        <v>-0.210332054964455</v>
       </c>
     </row>
     <row r="252">
@@ -3818,7 +3788,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.302447666327995</v>
+        <v>-0.325453231955208</v>
       </c>
     </row>
     <row r="253">
@@ -3829,7 +3799,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.112826582755134</v>
+        <v>-0.228195940634738</v>
       </c>
     </row>
     <row r="254">
@@ -3840,7 +3810,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.393426306086231</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="255">
@@ -3851,7 +3821,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.174563185180952</v>
+        <v>-0.169779502858334</v>
       </c>
     </row>
     <row r="256">
@@ -3862,7 +3832,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.444076339147596</v>
+        <v>-0.0987572112320434</v>
       </c>
     </row>
     <row r="257">
@@ -3873,7 +3843,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>0.500437421308113</v>
+        <v>0.270566684623616</v>
       </c>
     </row>
     <row r="258">
@@ -3884,7 +3854,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.302666693103089</v>
       </c>
     </row>
     <row r="259">
@@ -3895,7 +3865,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.295682166541314</v>
+        <v>-0.440615856378877</v>
       </c>
     </row>
     <row r="260">
@@ -3917,7 +3887,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.124801063592241</v>
+        <v>0.0759793784809901</v>
       </c>
     </row>
     <row r="262">
@@ -3939,7 +3909,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.172001015466338</v>
+        <v>-0.277530931978533</v>
       </c>
     </row>
     <row r="264">
@@ -3950,7 +3920,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.373390181728568</v>
+        <v>-0.445815672082878</v>
       </c>
     </row>
     <row r="265">
@@ -3961,7 +3931,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.464310807288325</v>
+        <v>-0.266215579604361</v>
       </c>
     </row>
     <row r="266">
@@ -3983,7 +3953,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.675987834050178</v>
+        <v>-1.93858877455574</v>
       </c>
     </row>
     <row r="268">
@@ -3994,7 +3964,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.280852393736797</v>
+        <v>-0.763914798266536</v>
       </c>
     </row>
     <row r="269">
@@ -4005,7 +3975,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.355771270436896</v>
+        <v>-0.240790825413178</v>
       </c>
     </row>
     <row r="270">
@@ -4016,7 +3986,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.364038398824554</v>
+        <v>-0.725694947741437</v>
       </c>
     </row>
     <row r="271">
@@ -4027,7 +3997,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.259390573556866</v>
+        <v>-0.881299692420642</v>
       </c>
     </row>
     <row r="272">
@@ -4038,7 +4008,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.244824138296603</v>
+        <v>-0.345693787142487</v>
       </c>
     </row>
     <row r="273">
@@ -4049,7 +4019,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.136234168549221</v>
+        <v>-0.319405980214334</v>
       </c>
     </row>
     <row r="274">
@@ -4060,7 +4030,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.501306160931297</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="275">
@@ -4071,7 +4041,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.390007741642503</v>
+        <v>-0.387276778754569</v>
       </c>
     </row>
     <row r="276">
@@ -4082,7 +4052,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.595889866981262</v>
+        <v>-0.388643646533915</v>
       </c>
     </row>
     <row r="277">
@@ -4104,7 +4074,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.266545613393487</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="279">
@@ -4115,7 +4085,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.260059952214046</v>
+        <v>-0.533614456174546</v>
       </c>
     </row>
     <row r="280">
@@ -4126,7 +4096,7 @@
         <v>16</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.390399585579927</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="281">
@@ -4137,7 +4107,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.386809758383032</v>
+        <v>-0.34884397849545</v>
       </c>
     </row>
     <row r="282">
@@ -4148,7 +4118,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.20761688324933</v>
       </c>
     </row>
     <row r="283">
@@ -4159,7 +4129,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.723106176357719</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="284">
@@ -4170,7 +4140,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.320018124744567</v>
       </c>
     </row>
     <row r="285">
@@ -4181,7 +4151,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.496602229988027</v>
+        <v>-0.383266784458379</v>
       </c>
     </row>
     <row r="286">
@@ -4192,7 +4162,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.332059372281162</v>
+        <v>-0.408657164105917</v>
       </c>
     </row>
     <row r="287">
@@ -4214,7 +4184,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.16844091888301</v>
+        <v>-0.227918411256894</v>
       </c>
     </row>
     <row r="289">
@@ -4225,7 +4195,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.565308999108018</v>
+        <v>-0.00120613422879479</v>
       </c>
     </row>
     <row r="290">
@@ -4236,7 +4206,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.0801846042318641</v>
+        <v>0.256346178613864</v>
       </c>
     </row>
     <row r="291">
@@ -4258,7 +4228,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.639434587718794</v>
+        <v>-0.544708483196046</v>
       </c>
     </row>
     <row r="293">
@@ -4269,7 +4239,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.293787551859055</v>
+        <v>-0.464244817451464</v>
       </c>
     </row>
     <row r="294">
@@ -4280,7 +4250,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.353583888421005</v>
       </c>
     </row>
     <row r="295">
@@ -4291,7 +4261,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.256098842080152</v>
+        <v>-0.254462072607389</v>
       </c>
     </row>
     <row r="296">
@@ -4302,7 +4272,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.192076104049955</v>
       </c>
     </row>
     <row r="297">
@@ -4313,7 +4283,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.45322060420542</v>
+        <v>-1.28043914733558</v>
       </c>
     </row>
     <row r="298">
@@ -4324,7 +4294,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.143392636742011</v>
+        <v>-0.500594249568952</v>
       </c>
     </row>
     <row r="299">
@@ -4335,7 +4305,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.21086864045874</v>
+        <v>-0.144522300582329</v>
       </c>
     </row>
     <row r="300">
@@ -4346,7 +4316,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.362052901657626</v>
+        <v>-0.325888984135327</v>
       </c>
     </row>
     <row r="301">
@@ -4357,7 +4327,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.307143634875802</v>
       </c>
     </row>
     <row r="302">
@@ -4368,7 +4338,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.715670348626512</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="303">
@@ -4379,7 +4349,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.267784870706377</v>
+        <v>-0.240107862080142</v>
       </c>
     </row>
     <row r="304">
@@ -4390,7 +4360,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.476984144301391</v>
+        <v>-0.328301783129978</v>
       </c>
     </row>
     <row r="305">
@@ -4434,7 +4404,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.198487524441091</v>
       </c>
     </row>
     <row r="309">
@@ -4445,7 +4415,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.15227145557063</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="310">
@@ -4456,7 +4426,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.574759695886101</v>
+        <v>-0.354807658690157</v>
       </c>
     </row>
     <row r="311">
@@ -4467,7 +4437,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.198080221405754</v>
+        <v>-0.23496053777051</v>
       </c>
     </row>
     <row r="312">
@@ -4478,7 +4448,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.662178099413699</v>
+        <v>-0.273205972011723</v>
       </c>
     </row>
     <row r="313">
@@ -4489,7 +4459,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>0.247411689601474</v>
+        <v>-0.0365398660282439</v>
       </c>
     </row>
     <row r="314">
@@ -4500,7 +4470,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.458576430022596</v>
+        <v>0.0162071090113685</v>
       </c>
     </row>
     <row r="315">
@@ -4511,7 +4481,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>0.0453057443926214</v>
+        <v>-0.190332614525375</v>
       </c>
     </row>
     <row r="316">
@@ -4522,7 +4492,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.211167380297593</v>
+        <v>-0.35966444631742</v>
       </c>
     </row>
     <row r="317">
@@ -4533,7 +4503,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.652046545835014</v>
+        <v>-0.464194272280073</v>
       </c>
     </row>
     <row r="318">
@@ -4544,7 +4514,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.948086505667884</v>
+        <v>-0.584085982630208</v>
       </c>
     </row>
     <row r="319">
@@ -4555,7 +4525,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.226117057255096</v>
+        <v>-0.222102772563285</v>
       </c>
     </row>
     <row r="320">
@@ -4577,7 +4547,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.267283803116934</v>
+        <v>-0.482798290038156</v>
       </c>
     </row>
     <row r="322">
@@ -4588,7 +4558,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.298805549675543</v>
+        <v>-0.471027145730764</v>
       </c>
     </row>
     <row r="323">
@@ -4599,7 +4569,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>0.151740051178724</v>
+        <v>0.193997030205831</v>
       </c>
     </row>
     <row r="324">
@@ -4610,7 +4580,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.358580039280117</v>
+        <v>0.230577238492707</v>
       </c>
     </row>
     <row r="325">
@@ -4621,7 +4591,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.258171592201617</v>
+        <v>-0.19859966552202</v>
       </c>
     </row>
     <row r="326">
@@ -4632,7 +4602,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-0.638359391376001</v>
+        <v>-0.536524553452491</v>
       </c>
     </row>
     <row r="327">
@@ -4654,7 +4624,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.182193267139765</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="329">
@@ -4676,7 +4646,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.478376287567412</v>
       </c>
     </row>
     <row r="331">
@@ -4687,7 +4657,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.333015181312796</v>
+        <v>-0.289085463205065</v>
       </c>
     </row>
     <row r="332">
@@ -4698,7 +4668,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.207913008694366</v>
       </c>
     </row>
     <row r="333">
@@ -4709,7 +4679,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.244793400090313</v>
+        <v>-0.16697074329226</v>
       </c>
     </row>
     <row r="334">
@@ -4720,7 +4690,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.116028428666242</v>
       </c>
     </row>
     <row r="335">
@@ -4731,7 +4701,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.471981431307231</v>
+        <v>-0.457580003402356</v>
       </c>
     </row>
     <row r="336">
@@ -4753,7 +4723,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.197698730019028</v>
+        <v>-1.57348887107132</v>
       </c>
     </row>
     <row r="338">
@@ -4775,7 +4745,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>0.323770442167248</v>
+        <v>-0.606215604682599</v>
       </c>
     </row>
     <row r="340">
@@ -4786,7 +4756,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.27083286028669</v>
       </c>
     </row>
     <row r="341">
@@ -4797,7 +4767,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.157101345014764</v>
+        <v>-0.176384859603638</v>
       </c>
     </row>
     <row r="342">
@@ -4808,7 +4778,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.226633505959851</v>
+        <v>-0.648667461083079</v>
       </c>
     </row>
     <row r="343">
@@ -4819,7 +4789,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.216266650450104</v>
+        <v>-0.209840873484949</v>
       </c>
     </row>
     <row r="344">
@@ -4830,7 +4800,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.169783476854605</v>
+        <v>-0.110845553104349</v>
       </c>
     </row>
     <row r="345">
@@ -4841,7 +4811,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.920362770073555</v>
+        <v>-1.0606875470698</v>
       </c>
     </row>
     <row r="346">
@@ -4852,7 +4822,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>0.207799853013469</v>
+        <v>0.288038674867249</v>
       </c>
     </row>
     <row r="347">
@@ -4874,7 +4844,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.487116348670316</v>
+        <v>-0.513262076572261</v>
       </c>
     </row>
     <row r="349">
@@ -4896,7 +4866,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.240283327764574</v>
+        <v>-0.114395767234462</v>
       </c>
     </row>
     <row r="351">
@@ -4907,7 +4877,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.345669074521566</v>
+        <v>-0.356943962422728</v>
       </c>
     </row>
     <row r="352">
@@ -4918,7 +4888,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.261121929546251</v>
+        <v>-0.276545422186942</v>
       </c>
     </row>
     <row r="353">
@@ -4929,7 +4899,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-1.05169076343484</v>
+        <v>-0.294945362529244</v>
       </c>
     </row>
     <row r="354">
@@ -4951,7 +4921,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.910552272310938</v>
+        <v>-1.3879808831237</v>
       </c>
     </row>
     <row r="356">
@@ -4962,7 +4932,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.495610828813724</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="357">
@@ -4984,7 +4954,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.890285489580693</v>
+        <v>-1.4819123973217</v>
       </c>
     </row>
     <row r="359">
@@ -4995,7 +4965,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.223609426739522</v>
+        <v>-0.187202371168597</v>
       </c>
     </row>
     <row r="360">
@@ -5006,7 +4976,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.161790759207088</v>
+        <v>-0.468100083005835</v>
       </c>
     </row>
     <row r="361">
@@ -5017,7 +4987,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.682191831600497</v>
+        <v>-0.602765356271478</v>
       </c>
     </row>
     <row r="362">
@@ -5028,7 +4998,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-1.01645258225264</v>
+        <v>-1.24397728614972</v>
       </c>
     </row>
     <row r="363">
@@ -5039,7 +5009,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.196875627862031</v>
+        <v>-0.295491855943667</v>
       </c>
     </row>
     <row r="364">
@@ -5050,7 +5020,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.209758925169211</v>
+        <v>-0.427199579829856</v>
       </c>
     </row>
     <row r="365">
@@ -5061,7 +5031,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.261868909312011</v>
+        <v>-0.0880197914312049</v>
       </c>
     </row>
     <row r="366">
@@ -5072,7 +5042,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.492512947763127</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="367">
@@ -5083,7 +5053,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.235654815970381</v>
+        <v>-0.606523228951172</v>
       </c>
     </row>
     <row r="368">
@@ -5094,7 +5064,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.0292183327341513</v>
+        <v>0.113043676047814</v>
       </c>
     </row>
     <row r="369">
@@ -5105,7 +5075,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.294640109365831</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="370">
@@ -5116,7 +5086,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.76010642404661</v>
       </c>
     </row>
     <row r="371">
@@ -5127,7 +5097,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.307907796903573</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="372">
@@ -5138,7 +5108,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.325316834916803</v>
+        <v>-0.24780445701466</v>
       </c>
     </row>
     <row r="373">
@@ -5149,7 +5119,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>0.516914278227868</v>
+        <v>0.154573095687958</v>
       </c>
     </row>
     <row r="374">
@@ -5160,7 +5130,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.0781008444488624</v>
+        <v>-0.496029539577687</v>
       </c>
     </row>
     <row r="375">
@@ -5171,7 +5141,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.170765796031607</v>
+        <v>-0.543161692218171</v>
       </c>
     </row>
     <row r="376">
@@ -5182,7 +5152,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.278094060230922</v>
+        <v>0.115842931233195</v>
       </c>
     </row>
     <row r="377">
@@ -5204,7 +5174,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.221451529409475</v>
       </c>
     </row>
     <row r="379">
@@ -5215,7 +5185,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.0858463990357472</v>
+        <v>-0.64333876089888</v>
       </c>
     </row>
     <row r="380">
@@ -5226,7 +5196,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.177257604327864</v>
+        <v>-0.175432806195559</v>
       </c>
     </row>
     <row r="381">
@@ -5237,7 +5207,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.139836017801676</v>
+        <v>-0.366727915198539</v>
       </c>
     </row>
     <row r="382">
@@ -5248,7 +5218,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.168470395567029</v>
+        <v>-0.230799472148535</v>
       </c>
     </row>
     <row r="383">
@@ -5270,7 +5240,7 @@
         <v>16</v>
       </c>
       <c r="C384" t="n">
-        <v>-0.222609760515893</v>
+        <v>-0.20789830201933</v>
       </c>
     </row>
     <row r="385">
@@ -5314,7 +5284,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.622053513910628</v>
+        <v>-0.438394653787623</v>
       </c>
     </row>
     <row r="389">
@@ -5325,7 +5295,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.349810744219339</v>
+        <v>-0.085351442082066</v>
       </c>
     </row>
     <row r="390">
@@ -5336,7 +5306,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.341699026635769</v>
+        <v>-0.348914472081456</v>
       </c>
     </row>
     <row r="391">
@@ -5347,7 +5317,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.0118491884265601</v>
+        <v>-0.224595392949061</v>
       </c>
     </row>
     <row r="392">
@@ -5358,7 +5328,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.353634236483721</v>
+        <v>-0.33345725213708</v>
       </c>
     </row>
     <row r="393">
@@ -5369,7 +5339,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.225917844585282</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="394">
@@ -5380,7 +5350,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.222376044752474</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="395">
@@ -5391,7 +5361,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.207969457061011</v>
+        <v>-0.241052747353623</v>
       </c>
     </row>
     <row r="396">
@@ -5413,7 +5383,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-0.538760867483549</v>
+        <v>-0.210267189026527</v>
       </c>
     </row>
     <row r="398">
@@ -5424,7 +5394,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.418849226936639</v>
+        <v>-0.51799134244334</v>
       </c>
     </row>
     <row r="399">
@@ -5446,7 +5416,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.536833212818893</v>
+        <v>-0.843747860266169</v>
       </c>
     </row>
     <row r="401">
@@ -5457,7 +5427,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-0.311172112958843</v>
+        <v>-0.290335697990778</v>
       </c>
     </row>
     <row r="402">
@@ -5512,7 +5482,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.196894346640815</v>
+        <v>-0.169937967737063</v>
       </c>
     </row>
     <row r="407">
@@ -5523,7 +5493,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.468776483706997</v>
+        <v>-1.15970963790633</v>
       </c>
     </row>
     <row r="408">
@@ -5534,7 +5504,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.23328439672542</v>
       </c>
     </row>
     <row r="409">
@@ -5545,7 +5515,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.367174941136412</v>
+        <v>-0.850722628795225</v>
       </c>
     </row>
     <row r="410">
@@ -5556,7 +5526,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.574590365233641</v>
       </c>
     </row>
     <row r="411">
@@ -5567,7 +5537,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.231144453825589</v>
+        <v>-0.331856146478118</v>
       </c>
     </row>
     <row r="412">
@@ -5578,7 +5548,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.662933423920988</v>
+        <v>-0.212475682526196</v>
       </c>
     </row>
     <row r="413">
@@ -5589,7 +5559,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.211471878441321</v>
+        <v>-0.227827751610682</v>
       </c>
     </row>
     <row r="414">
@@ -5611,7 +5581,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.0724785280168714</v>
+        <v>-0.00252388900556499</v>
       </c>
     </row>
     <row r="416">
@@ -5622,7 +5592,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.293115023313224</v>
+        <v>0.0403148307571504</v>
       </c>
     </row>
     <row r="417">
@@ -5633,7 +5603,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>0.130035365301328</v>
+        <v>0.295670189316023</v>
       </c>
     </row>
     <row r="418">
@@ -5644,7 +5614,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.845180445069682</v>
+        <v>-0.545774236484936</v>
       </c>
     </row>
     <row r="419">
@@ -5655,7 +5625,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.273254143277339</v>
+        <v>-0.301598995129137</v>
       </c>
     </row>
     <row r="420">
@@ -5666,7 +5636,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.199273145137384</v>
       </c>
     </row>
     <row r="421">
@@ -5677,7 +5647,7 @@
         <v>16</v>
       </c>
       <c r="C421" t="n">
-        <v>-0.174299324402225</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="422">
@@ -5688,7 +5658,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-0.329580774923057</v>
+        <v>-0.280150266448189</v>
       </c>
     </row>
     <row r="423">
@@ -5710,7 +5680,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.206941090406077</v>
+        <v>-0.34560589810705</v>
       </c>
     </row>
     <row r="425">
@@ -5721,7 +5691,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.195696987531379</v>
+        <v>-0.155567548271853</v>
       </c>
     </row>
     <row r="426">
@@ -5732,7 +5702,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>0.448185807181582</v>
+        <v>0.471612710205291</v>
       </c>
     </row>
     <row r="427">
@@ -5743,7 +5713,7 @@
         <v>16</v>
       </c>
       <c r="C427" t="n">
-        <v>-0.354045276713511</v>
+        <v>-0.392513612673361</v>
       </c>
     </row>
     <row r="428">
@@ -5754,7 +5724,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.13066514190515</v>
+        <v>-0.239008910189454</v>
       </c>
     </row>
     <row r="429">
@@ -5765,7 +5735,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.568849637369696</v>
+        <v>-0.539359382678948</v>
       </c>
     </row>
     <row r="430">
@@ -5776,7 +5746,7 @@
         <v>16</v>
       </c>
       <c r="C430" t="n">
-        <v>-0.91328862712454</v>
+        <v>-0.450410215493781</v>
       </c>
     </row>
     <row r="431">
@@ -5787,7 +5757,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.418222207267719</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="432">
@@ -5798,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.208000321293845</v>
       </c>
     </row>
     <row r="433">
@@ -5809,7 +5779,7 @@
         <v>16</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.388196999139267</v>
+        <v>-0.88056491550676</v>
       </c>
     </row>
     <row r="434">
@@ -5820,7 +5790,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.747507548240767</v>
+        <v>-0.177268347330309</v>
       </c>
     </row>
     <row r="435">
@@ -5831,7 +5801,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>0.0639661358847242</v>
+        <v>-0.0797959727602411</v>
       </c>
     </row>
     <row r="436">
@@ -5842,7 +5812,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.245910801708257</v>
       </c>
     </row>
     <row r="437">
@@ -5864,7 +5834,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0663940296186671</v>
+        <v>-0.218469711586553</v>
       </c>
     </row>
     <row r="439">
@@ -5875,7 +5845,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.384249362830389</v>
       </c>
     </row>
     <row r="440">
@@ -5886,7 +5856,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.176666746095935</v>
+        <v>-0.17869631861613</v>
       </c>
     </row>
     <row r="441">
@@ -5897,7 +5867,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.250672282842935</v>
+        <v>-0.223169366735388</v>
       </c>
     </row>
     <row r="442">
@@ -5930,7 +5900,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-1.12099136144192</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="445">
@@ -5941,7 +5911,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.159107311432924</v>
+        <v>-0.173064148547483</v>
       </c>
     </row>
     <row r="446">
@@ -5952,7 +5922,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.135362274260501</v>
+        <v>0.138560310260848</v>
       </c>
     </row>
     <row r="447">
@@ -5974,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.175053636363699</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="449">
@@ -5985,7 +5955,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.200444950704833</v>
+        <v>-0.361775447632802</v>
       </c>
     </row>
     <row r="450">
@@ -6007,7 +5977,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.149856627473266</v>
+        <v>-0.0868763839401645</v>
       </c>
     </row>
     <row r="452">
@@ -6018,7 +5988,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.338522034558865</v>
+        <v>-0.357628616623304</v>
       </c>
     </row>
     <row r="453">
@@ -6029,7 +5999,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.178833765488992</v>
+        <v>-0.167041913020884</v>
       </c>
     </row>
     <row r="454">
@@ -6040,7 +6010,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.278786035657778</v>
       </c>
     </row>
     <row r="455">
@@ -6051,7 +6021,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.35433324330937</v>
+        <v>-0.396703840536641</v>
       </c>
     </row>
     <row r="456">
@@ -6062,7 +6032,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.183152673545179</v>
+        <v>0.180889389453492</v>
       </c>
     </row>
     <row r="457">
@@ -6073,7 +6043,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>0.237270174253564</v>
+        <v>0.19654436899832</v>
       </c>
     </row>
     <row r="458">
@@ -6084,7 +6054,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.36658268469502</v>
+        <v>-0.344495911662076</v>
       </c>
     </row>
     <row r="459">
@@ -6117,7 +6087,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.129459061566874</v>
+        <v>-0.379620163050706</v>
       </c>
     </row>
     <row r="462">
@@ -6139,7 +6109,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.167782577729248</v>
+        <v>-0.242304663318625</v>
       </c>
     </row>
     <row r="464">
@@ -6150,7 +6120,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.325927350332286</v>
+        <v>-0.391275301069971</v>
       </c>
     </row>
     <row r="465">
@@ -6161,7 +6131,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.240727634021624</v>
+        <v>-0.157477956439186</v>
       </c>
     </row>
     <row r="466">
@@ -6172,7 +6142,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.37334187639371</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="467">
@@ -6183,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.684813527872917</v>
+        <v>-1.32305338098901</v>
       </c>
     </row>
     <row r="468">
@@ -6194,7 +6164,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.75080735078276</v>
+        <v>-0.325819636079872</v>
       </c>
     </row>
     <row r="469">
@@ -6205,7 +6175,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.331779785904323</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="470">
@@ -6216,7 +6186,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-1.04990578483127</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="471">
@@ -6227,7 +6197,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.33238844408201</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="472">
@@ -6249,7 +6219,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.2777472192151</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="474">
@@ -6260,7 +6230,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.390633736737933</v>
       </c>
     </row>
     <row r="475">
@@ -6282,7 +6252,7 @@
         <v>16</v>
       </c>
       <c r="C476" t="n">
-        <v>-0.1631268360896</v>
+        <v>-0.406261182225188</v>
       </c>
     </row>
     <row r="477">
@@ -6304,7 +6274,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.240453035367345</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="479">
@@ -6315,7 +6285,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.340544325018328</v>
+        <v>-0.331143010719072</v>
       </c>
     </row>
     <row r="480">
@@ -6326,7 +6296,7 @@
         <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>-0.252589906092801</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="481">
@@ -6337,7 +6307,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.750412036859804</v>
+        <v>-0.221556822661074</v>
       </c>
     </row>
     <row r="482">
@@ -6359,7 +6329,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.891333972231982</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="484">
@@ -6370,7 +6340,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.349915250884021</v>
       </c>
     </row>
     <row r="485">
@@ -6381,7 +6351,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.281387605855704</v>
+        <v>-0.490395943153897</v>
       </c>
     </row>
     <row r="486">
@@ -6392,7 +6362,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.4157018821992</v>
+        <v>-0.373424040779592</v>
       </c>
     </row>
     <row r="487">
@@ -6414,7 +6384,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>0.127466137220061</v>
+        <v>-0.219095087438</v>
       </c>
     </row>
     <row r="489">
@@ -6425,7 +6395,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.225275891500805</v>
+        <v>-0.409629507898967</v>
       </c>
     </row>
     <row r="490">
@@ -6436,7 +6406,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.302718899968052</v>
+        <v>-0.0570451227098283</v>
       </c>
     </row>
     <row r="491">
@@ -6458,7 +6428,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.819662241103333</v>
+        <v>-0.492152710666336</v>
       </c>
     </row>
     <row r="493">
@@ -6469,7 +6439,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.0422206661638826</v>
+        <v>-0.342813687885609</v>
       </c>
     </row>
     <row r="494">
@@ -6480,7 +6450,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.377078812926327</v>
+        <v>-0.0863084674017742</v>
       </c>
     </row>
     <row r="495">
@@ -6491,7 +6461,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.195097554092058</v>
+        <v>-0.21591646513405</v>
       </c>
     </row>
     <row r="496">
@@ -6513,7 +6483,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.395841574680976</v>
+        <v>-0.709449969422949</v>
       </c>
     </row>
     <row r="498">
@@ -6524,7 +6494,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.609368559298373</v>
+        <v>-1.08962136049465</v>
       </c>
     </row>
     <row r="499">
@@ -6535,7 +6505,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.350741866636073</v>
+        <v>-0.354184567941697</v>
       </c>
     </row>
     <row r="500">
@@ -6546,7 +6516,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.309574184355366</v>
+        <v>-0.284315137177994</v>
       </c>
     </row>
     <row r="501">
@@ -6557,7 +6527,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.175232946693879</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="502">
@@ -6590,7 +6560,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.0758823857882498</v>
+        <v>0.478892421305992</v>
       </c>
     </row>
     <row r="505">
@@ -6612,7 +6582,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.26013473196264</v>
       </c>
     </row>
     <row r="507">
@@ -6634,7 +6604,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.0661606945931992</v>
+        <v>-0.15580869957376</v>
       </c>
     </row>
     <row r="509">
@@ -6645,7 +6615,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.716819370272186</v>
       </c>
     </row>
     <row r="510">
@@ -6656,7 +6626,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.34953412645332</v>
+        <v>-0.526117536552001</v>
       </c>
     </row>
     <row r="511">
@@ -6667,7 +6637,7 @@
         <v>16</v>
       </c>
       <c r="C511" t="n">
-        <v>-0.200267216017664</v>
+        <v>-0.201181181535585</v>
       </c>
     </row>
     <row r="512">
@@ -6678,7 +6648,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.248674205655999</v>
+        <v>-0.285262895611395</v>
       </c>
     </row>
     <row r="513">
@@ -6689,7 +6659,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>0.67195046066665</v>
+        <v>0.0971278312501609</v>
       </c>
     </row>
     <row r="514">
@@ -6700,7 +6670,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.275354263952629</v>
+        <v>-0.388900472540107</v>
       </c>
     </row>
     <row r="515">
@@ -6711,7 +6681,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>0.153679779679725</v>
+        <v>-0.366093407434688</v>
       </c>
     </row>
     <row r="516">
@@ -6722,7 +6692,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.200522566154086</v>
+        <v>-0.239894634915587</v>
       </c>
     </row>
     <row r="517">
@@ -6744,7 +6714,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.713567315376341</v>
+        <v>-0.664535904199868</v>
       </c>
     </row>
     <row r="519">
@@ -6755,7 +6725,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.173899166235574</v>
+        <v>-0.271924068034712</v>
       </c>
     </row>
     <row r="520">
@@ -6777,7 +6747,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.279868063839614</v>
+        <v>-0.313381825580965</v>
       </c>
     </row>
     <row r="522">
@@ -6788,7 +6758,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.304991217616104</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="523">
@@ -6799,7 +6769,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>0.334555295054379</v>
+        <v>0.308118760875781</v>
       </c>
     </row>
     <row r="524">
@@ -6810,7 +6780,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>0.103482115142107</v>
+        <v>0.330995951875287</v>
       </c>
     </row>
     <row r="525">
@@ -6832,7 +6802,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-0.85982436895639</v>
+        <v>-1.00275629270273</v>
       </c>
     </row>
     <row r="527">
@@ -6854,7 +6824,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.348753600209381</v>
+        <v>-1.40216570901283</v>
       </c>
     </row>
     <row r="529">
@@ -6876,7 +6846,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.39826774401009</v>
+        <v>-0.411249986486822</v>
       </c>
     </row>
     <row r="531">
@@ -6887,7 +6857,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.40454677787699</v>
+        <v>-0.290266547277556</v>
       </c>
     </row>
     <row r="532">
@@ -6898,7 +6868,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.159750190376495</v>
+        <v>-0.247261363935098</v>
       </c>
     </row>
     <row r="533">
@@ -6920,7 +6890,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.303448334036468</v>
       </c>
     </row>
     <row r="535">
@@ -6931,7 +6901,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.258178154640863</v>
+        <v>-0.264255724157938</v>
       </c>
     </row>
     <row r="536">
@@ -6953,7 +6923,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.436766681252384</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="538">
@@ -6975,7 +6945,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>0.08443411659998</v>
+        <v>-0.406925007630646</v>
       </c>
     </row>
     <row r="540">
@@ -6986,7 +6956,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.07349962161139</v>
       </c>
     </row>
     <row r="541">
@@ -6997,7 +6967,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.241491628271609</v>
+        <v>-0.274282701019111</v>
       </c>
     </row>
     <row r="542">
@@ -7008,7 +6978,7 @@
         <v>16</v>
       </c>
       <c r="C542" t="n">
-        <v>-0.57094717225744</v>
+        <v>-0.839379565634924</v>
       </c>
     </row>
     <row r="543">
@@ -7019,7 +6989,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.182653784212757</v>
+        <v>-0.189163813329871</v>
       </c>
     </row>
     <row r="544">
@@ -7030,7 +7000,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.187799525482622</v>
+        <v>-0.467392728136291</v>
       </c>
     </row>
     <row r="545">
@@ -7041,7 +7011,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-1.89613739552031</v>
+        <v>-1.15357785163423</v>
       </c>
     </row>
     <row r="546">
@@ -7052,7 +7022,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.195170182075148</v>
+        <v>-0.130951667115695</v>
       </c>
     </row>
     <row r="547">
@@ -7074,7 +7044,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-0.274591602936259</v>
+        <v>-0.128934204526507</v>
       </c>
     </row>
     <row r="549">
@@ -7085,7 +7055,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.334779050378226</v>
+        <v>-0.21789767777222</v>
       </c>
     </row>
     <row r="550">
@@ -7096,7 +7066,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.23447403730438</v>
+        <v>-0.117940711469662</v>
       </c>
     </row>
     <row r="551">
@@ -7118,7 +7088,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.366623743659748</v>
+        <v>-0.595103186210002</v>
       </c>
     </row>
     <row r="553">
@@ -7129,7 +7099,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.975806002188532</v>
+        <v>-0.257567176277901</v>
       </c>
     </row>
     <row r="554">
@@ -7140,7 +7110,7 @@
         <v>16</v>
       </c>
       <c r="C554" t="n">
-        <v>-0.203836287373627</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="555">
@@ -7151,7 +7121,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.367072378286655</v>
+        <v>-1.33307721542606</v>
       </c>
     </row>
     <row r="556">
@@ -7162,7 +7132,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-0.711616107160864</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="557">
@@ -7184,7 +7154,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.637543932616592</v>
       </c>
     </row>
     <row r="559">
@@ -7195,7 +7165,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>0.00592804757056875</v>
+        <v>-0.304796806419715</v>
       </c>
     </row>
     <row r="560">
@@ -7206,7 +7176,7 @@
         <v>16</v>
       </c>
       <c r="C560" t="n">
-        <v>0.12678830396428</v>
+        <v>-0.331673109054565</v>
       </c>
     </row>
     <row r="561">
@@ -7217,7 +7187,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.252542678669807</v>
+        <v>-0.559799945634094</v>
       </c>
     </row>
     <row r="562">
@@ -7228,7 +7198,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.209739846236503</v>
+        <v>-0.781204805352768</v>
       </c>
     </row>
     <row r="563">
@@ -7239,7 +7209,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.0561774017544805</v>
+        <v>0.0544449538441116</v>
       </c>
     </row>
     <row r="564">
@@ -7261,7 +7231,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.189765438300964</v>
+        <v>-0.0939147829386326</v>
       </c>
     </row>
     <row r="566">
@@ -7294,7 +7264,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.289686611241617</v>
+        <v>-0.105016215053814</v>
       </c>
     </row>
     <row r="569">
@@ -7305,7 +7275,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.289431317701757</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="570">
@@ -7327,7 +7297,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.384087880198624</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="572">
@@ -7349,7 +7319,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.403506061097239</v>
+        <v>-0.340801516513916</v>
       </c>
     </row>
     <row r="574">
@@ -7360,7 +7330,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.236829037915917</v>
+        <v>-0.312687007596476</v>
       </c>
     </row>
     <row r="575">
@@ -7371,7 +7341,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.0861654251963213</v>
+        <v>-0.877082889308189</v>
       </c>
     </row>
     <row r="576">
@@ -7382,7 +7352,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.284129307221363</v>
+        <v>-0.247251335753698</v>
       </c>
     </row>
     <row r="577">
@@ -7404,7 +7374,7 @@
         <v>16</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.20398346456168</v>
+        <v>-0.282205315480822</v>
       </c>
     </row>
     <row r="579">
@@ -7415,7 +7385,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.255599829800979</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="580">
@@ -7426,7 +7396,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.169775692399419</v>
+        <v>-0.151147579020245</v>
       </c>
     </row>
     <row r="581">
@@ -7437,7 +7407,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.218026911307233</v>
+        <v>-0.312267070491296</v>
       </c>
     </row>
     <row r="582">
@@ -7448,7 +7418,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.332379178949304</v>
       </c>
     </row>
     <row r="583">
@@ -7470,7 +7440,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.338405056374625</v>
       </c>
     </row>
     <row r="585">
@@ -7481,7 +7451,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.242308731979525</v>
       </c>
     </row>
     <row r="586">
@@ -7525,7 +7495,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.207910835626302</v>
+        <v>-0.195226277158393</v>
       </c>
     </row>
     <row r="590">
@@ -7536,7 +7506,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.347286410260301</v>
+        <v>-0.34561703755572</v>
       </c>
     </row>
     <row r="591">
@@ -7547,7 +7517,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.0861274127822087</v>
+        <v>-0.189091520097009</v>
       </c>
     </row>
     <row r="592">
@@ -7558,7 +7528,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.330310950521463</v>
+        <v>-0.303896148877873</v>
       </c>
     </row>
     <row r="593">
@@ -7580,7 +7550,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.348126117747892</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="595">
@@ -7591,7 +7561,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.25546119864201</v>
       </c>
     </row>
     <row r="596">
@@ -7613,7 +7583,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.400567630199213</v>
+        <v>-0.329518707358531</v>
       </c>
     </row>
     <row r="598">
@@ -7624,7 +7594,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.383772459865023</v>
+        <v>-0.439704382605279</v>
       </c>
     </row>
     <row r="599">
@@ -7635,7 +7605,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.17258224490819</v>
       </c>
     </row>
     <row r="600">
@@ -7646,7 +7616,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.54082394160553</v>
+        <v>-0.33105265683318</v>
       </c>
     </row>
     <row r="601">
@@ -7657,7 +7627,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.316773788651127</v>
+        <v>-0.417821663903915</v>
       </c>
     </row>
     <row r="602">
@@ -7679,7 +7649,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.434233371344698</v>
+        <v>-0.277688730777729</v>
       </c>
     </row>
     <row r="604">
@@ -7690,7 +7660,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>0.122237668335373</v>
+        <v>-0.154819879747995</v>
       </c>
     </row>
     <row r="605">
@@ -7701,7 +7671,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.743653946413976</v>
+        <v>-0.616068696108589</v>
       </c>
     </row>
     <row r="606">
@@ -7723,7 +7693,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.396953007721068</v>
+        <v>-0.358180108207378</v>
       </c>
     </row>
     <row r="608">
@@ -7756,7 +7726,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.128147912943086</v>
+        <v>-0.16577754401175</v>
       </c>
     </row>
     <row r="611">
@@ -7767,7 +7737,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.520806654778599</v>
+        <v>-0.398970359633992</v>
       </c>
     </row>
     <row r="612">
@@ -7778,7 +7748,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.265508657198382</v>
+        <v>-0.0200718495829286</v>
       </c>
     </row>
     <row r="613">
@@ -7789,7 +7759,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.786255802843431</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="614">
@@ -7800,7 +7770,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.365238613641897</v>
       </c>
     </row>
     <row r="615">
@@ -7822,7 +7792,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.185604016462744</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="617">
@@ -7833,7 +7803,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.388903228995402</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="618">
@@ -7844,7 +7814,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.622445961534622</v>
+        <v>-0.305716449937172</v>
       </c>
     </row>
     <row r="619">
@@ -7855,7 +7825,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.444525034289787</v>
       </c>
     </row>
     <row r="620">
@@ -7866,7 +7836,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.32643504960934</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="621">
@@ -7888,7 +7858,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.279324376592379</v>
+        <v>-0.275294610554642</v>
       </c>
     </row>
     <row r="623">
@@ -7899,7 +7869,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.296683727270284</v>
+        <v>-0.346850420980242</v>
       </c>
     </row>
     <row r="624">
@@ -7910,7 +7880,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.312893588040435</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="625">
@@ -7932,7 +7902,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.173657188018812</v>
+        <v>-0.654071836058838</v>
       </c>
     </row>
     <row r="627">
@@ -7943,7 +7913,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.255222016280169</v>
+        <v>-0.206453102845358</v>
       </c>
     </row>
     <row r="628">
@@ -7954,7 +7924,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.189842639356856</v>
+        <v>-0.13712751500967</v>
       </c>
     </row>
     <row r="629">
@@ -7965,7 +7935,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.272204394354157</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="630">
@@ -7998,7 +7968,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.185701351021862</v>
+        <v>-0.222563144173759</v>
       </c>
     </row>
     <row r="633">
@@ -8020,7 +7990,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.256587685503628</v>
+        <v>-0.15600377136233</v>
       </c>
     </row>
     <row r="635">
@@ -8031,7 +8001,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.398744035228313</v>
+        <v>-0.595355461558494</v>
       </c>
     </row>
     <row r="636">
@@ -8042,7 +8012,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.432967213863527</v>
+        <v>-0.28674902049022</v>
       </c>
     </row>
     <row r="637">
@@ -8053,7 +8023,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.426465359896592</v>
+        <v>-0.503944506397116</v>
       </c>
     </row>
     <row r="638">
@@ -8064,7 +8034,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.191205522613788</v>
+        <v>-0.496076082023031</v>
       </c>
     </row>
     <row r="639">
@@ -8097,7 +8067,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.52034384762973</v>
+        <v>-0.494686091607249</v>
       </c>
     </row>
     <row r="642">
@@ -8108,7 +8078,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-1.06716318891249</v>
+        <v>-0.643563842222165</v>
       </c>
     </row>
     <row r="643">
@@ -8119,7 +8089,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.571546389178737</v>
+        <v>-0.290536976561871</v>
       </c>
     </row>
     <row r="644">
@@ -8130,7 +8100,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.300795798938362</v>
       </c>
     </row>
     <row r="645">
@@ -8152,7 +8122,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.290671328844976</v>
+        <v>-0.437604947799382</v>
       </c>
     </row>
     <row r="647">
@@ -8163,7 +8133,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.320960878973075</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="648">
@@ -8174,7 +8144,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>0.445084582144496</v>
+        <v>-0.0306537722524818</v>
       </c>
     </row>
     <row r="649">
@@ -8185,7 +8155,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>0.0608457001547748</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="650">
@@ -8196,7 +8166,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-0.158663753832465</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="651">
@@ -8218,7 +8188,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.178422392016428</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="653">
@@ -8229,7 +8199,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.263026559876482</v>
+        <v>-0.136197059847318</v>
       </c>
     </row>
     <row r="654">
@@ -8240,7 +8210,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.39768487866284</v>
+        <v>-0.462983519780044</v>
       </c>
     </row>
     <row r="655">
@@ -8251,7 +8221,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.188767504905715</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="656">
@@ -8262,7 +8232,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-0.291272764223281</v>
+        <v>-0.310691868646792</v>
       </c>
     </row>
     <row r="657">
@@ -8284,7 +8254,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.386142959620602</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="659">
@@ -8295,7 +8265,7 @@
         <v>16</v>
       </c>
       <c r="C659" t="n">
-        <v>-0.212520969550912</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="660">
@@ -8317,7 +8287,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>0.274003350040701</v>
+        <v>-0.0653507642909079</v>
       </c>
     </row>
     <row r="662">
@@ -8328,7 +8298,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.200500718550802</v>
+        <v>-0.247604194289675</v>
       </c>
     </row>
     <row r="663">
@@ -8339,7 +8309,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.213974361413849</v>
+        <v>-0.0288452083603981</v>
       </c>
     </row>
     <row r="664">
@@ -8361,7 +8331,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-1.40177184396613</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="666">
@@ -8372,7 +8342,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.569690081359956</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="667">
@@ -8383,7 +8353,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.28849193023657</v>
+        <v>-0.1188799331179</v>
       </c>
     </row>
     <row r="668">
@@ -8394,7 +8364,7 @@
         <v>16</v>
       </c>
       <c r="C668" t="n">
-        <v>-0.189523770074822</v>
+        <v>-0.280756615844984</v>
       </c>
     </row>
     <row r="669">
@@ -8405,7 +8375,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.356775721957022</v>
+        <v>-0.227086562629685</v>
       </c>
     </row>
     <row r="670">
@@ -8416,7 +8386,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>0.151592155230311</v>
+        <v>-0.145425014001628</v>
       </c>
     </row>
     <row r="671">
@@ -8427,7 +8397,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>0.267645371434474</v>
+        <v>0.165774218183361</v>
       </c>
     </row>
     <row r="672">
@@ -8438,7 +8408,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>0.248515740240528</v>
+        <v>-0.407206333793266</v>
       </c>
     </row>
     <row r="673">
@@ -8460,7 +8430,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.406175123916532</v>
+        <v>-0.969735166339816</v>
       </c>
     </row>
     <row r="675">
@@ -8471,7 +8441,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.0585345281862313</v>
+        <v>-0.585457676007213</v>
       </c>
     </row>
     <row r="676">
@@ -8493,7 +8463,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.360706129843256</v>
+        <v>-0.869426757718514</v>
       </c>
     </row>
     <row r="678">
@@ -8504,7 +8474,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.295766135066874</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="679">
@@ -8515,7 +8485,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.111468972210584</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="680">
@@ -8537,7 +8507,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.171640092763774</v>
       </c>
     </row>
     <row r="682">
@@ -8570,7 +8540,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.567931109939559</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="685">
@@ -8581,7 +8551,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.436294480624197</v>
       </c>
     </row>
     <row r="686">
@@ -8614,7 +8584,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.928316967890403</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="689">
@@ -8625,7 +8595,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.0109138770289425</v>
+        <v>-0.140106328765965</v>
       </c>
     </row>
     <row r="690">
@@ -8636,7 +8606,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.230302294448989</v>
+        <v>-0.217922455661326</v>
       </c>
     </row>
     <row r="691">
@@ -8647,7 +8617,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.186214503945711</v>
+        <v>-0.165230447880472</v>
       </c>
     </row>
     <row r="692">
@@ -8658,7 +8628,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.34661324900879</v>
       </c>
     </row>
     <row r="693">
@@ -8669,7 +8639,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.186196376041738</v>
+        <v>-0.633777194076845</v>
       </c>
     </row>
     <row r="694">
@@ -8680,7 +8650,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.395701582345061</v>
+        <v>-0.149224922189835</v>
       </c>
     </row>
     <row r="695">
@@ -8702,7 +8672,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.257905000633246</v>
+        <v>0.0119451720154757</v>
       </c>
     </row>
     <row r="697">
@@ -8713,7 +8683,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.182983501374865</v>
+        <v>-0.103047097000803</v>
       </c>
     </row>
     <row r="698">
@@ -8724,7 +8694,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.254807090859853</v>
+        <v>-0.369931116240438</v>
       </c>
     </row>
     <row r="699">
@@ -8735,7 +8705,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.297168461517257</v>
       </c>
     </row>
     <row r="700">
@@ -8757,7 +8727,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.22179661108085</v>
+        <v>-0.238273126563079</v>
       </c>
     </row>
     <row r="702">
@@ -8768,7 +8738,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.10015397251645</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="703">
@@ -8779,7 +8749,7 @@
         <v>16</v>
       </c>
       <c r="C703" t="n">
-        <v>-0.319268220020688</v>
+        <v>-0.412286766935499</v>
       </c>
     </row>
     <row r="704">
@@ -8790,7 +8760,7 @@
         <v>16</v>
       </c>
       <c r="C704" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.40204318050881</v>
       </c>
     </row>
     <row r="705">
@@ -8801,7 +8771,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.132165879749964</v>
       </c>
     </row>
     <row r="706">
@@ -8823,7 +8793,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.38765586347465</v>
+        <v>-0.347702263645042</v>
       </c>
     </row>
     <row r="708">
@@ -8834,7 +8804,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>0.358742743032982</v>
+        <v>0.275351130499281</v>
       </c>
     </row>
     <row r="709">
@@ -8845,7 +8815,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.26083907208631</v>
       </c>
     </row>
     <row r="710">
@@ -8856,7 +8826,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.454186761850815</v>
+        <v>-0.401845110767125</v>
       </c>
     </row>
     <row r="711">
@@ -8867,7 +8837,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.32317965174153</v>
+        <v>-0.278948536564924</v>
       </c>
     </row>
     <row r="712">
@@ -8878,7 +8848,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.183838433292484</v>
+        <v>-0.149483121996046</v>
       </c>
     </row>
     <row r="713">
@@ -8889,7 +8859,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.485305216257108</v>
+        <v>-0.185958250730327</v>
       </c>
     </row>
     <row r="714">
@@ -8900,7 +8870,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.380711799715851</v>
+        <v>-0.469708173732559</v>
       </c>
     </row>
     <row r="715">
@@ -8911,7 +8881,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.679728248561137</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="716">
@@ -8922,7 +8892,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.502032204403859</v>
+        <v>-0.453968067619088</v>
       </c>
     </row>
     <row r="717">
@@ -8933,7 +8903,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.5994090063346</v>
+        <v>-0.3689539996521</v>
       </c>
     </row>
     <row r="718">
@@ -8944,7 +8914,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.0661971354801509</v>
+        <v>-0.217448124749851</v>
       </c>
     </row>
     <row r="719">
@@ -8955,7 +8925,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>0.078620057321221</v>
+        <v>0.143831505841551</v>
       </c>
     </row>
     <row r="720">
@@ -8966,7 +8936,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.117110513137334</v>
+        <v>-0.932026112569067</v>
       </c>
     </row>
     <row r="721">
@@ -8977,7 +8947,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.249878870199543</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="722">
@@ -8999,7 +8969,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.3680595288137</v>
+        <v>-0.406277850393309</v>
       </c>
     </row>
     <row r="724">
@@ -9010,7 +8980,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.161390196344211</v>
+        <v>-0.118476771512358</v>
       </c>
     </row>
     <row r="725">
@@ -9043,7 +9013,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.193354166796313</v>
+        <v>-0.193282296132684</v>
       </c>
     </row>
     <row r="728">
@@ -9065,7 +9035,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>-0.457692643209187</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="730">
@@ -9076,7 +9046,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.157465400885834</v>
+        <v>-0.0483779433561811</v>
       </c>
     </row>
     <row r="731">
@@ -9087,7 +9057,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.316513380430609</v>
+        <v>-0.340785076121652</v>
       </c>
     </row>
     <row r="732">
@@ -9098,7 +9068,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-1.17665990534619</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="733">
@@ -9120,7 +9090,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.388233205979838</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="735">
@@ -9131,7 +9101,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.175834697128431</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="736">
@@ -9153,7 +9123,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.332046608172697</v>
+        <v>-0.511059083395057</v>
       </c>
     </row>
     <row r="738">
@@ -9186,7 +9156,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.445679614914518</v>
+        <v>-0.489046437859534</v>
       </c>
     </row>
     <row r="741">
@@ -9197,7 +9167,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.218116059144242</v>
       </c>
     </row>
     <row r="742">
@@ -9208,7 +9178,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.545918125416986</v>
+        <v>-0.772025911372839</v>
       </c>
     </row>
     <row r="743">
@@ -9219,7 +9189,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.714789346862933</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="744">
@@ -9230,7 +9200,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-0.219341139973369</v>
+        <v>-0.223490355293592</v>
       </c>
     </row>
     <row r="745">
@@ -9241,7 +9211,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.175952969736798</v>
+        <v>-0.188280057400523</v>
       </c>
     </row>
     <row r="746">
@@ -9252,7 +9222,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.685459243721529</v>
       </c>
     </row>
     <row r="747">
@@ -9263,7 +9233,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.237402818416896</v>
+        <v>-0.290523069606523</v>
       </c>
     </row>
     <row r="748">
@@ -9274,7 +9244,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.184213926038696</v>
+        <v>-0.221519027796323</v>
       </c>
     </row>
     <row r="749">
@@ -9296,7 +9266,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.416923963346924</v>
+        <v>-0.365947826844798</v>
       </c>
     </row>
     <row r="751">
@@ -9307,7 +9277,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.647890541689188</v>
+        <v>-0.819362911133533</v>
       </c>
     </row>
     <row r="752">
@@ -9318,7 +9288,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>0.255130283661997</v>
+        <v>0.00926942546087539</v>
       </c>
     </row>
     <row r="753">
@@ -9329,7 +9299,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.12542739598524</v>
+        <v>-0.161373898337535</v>
       </c>
     </row>
     <row r="754">
@@ -9340,7 +9310,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.258761725276491</v>
+        <v>-0.198949157443325</v>
       </c>
     </row>
     <row r="755">
@@ -9373,7 +9343,7 @@
         <v>16</v>
       </c>
       <c r="C757" t="n">
-        <v>-0.145465465180545</v>
+        <v>-0.0114199627868419</v>
       </c>
     </row>
     <row r="758">
@@ -9406,7 +9376,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.319359331844204</v>
+        <v>-0.263098890537061</v>
       </c>
     </row>
     <row r="761">
@@ -9417,7 +9387,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.396542046681135</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="762">
@@ -9428,7 +9398,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>0.0483430689946397</v>
+        <v>0.00481563381202832</v>
       </c>
     </row>
     <row r="763">
@@ -9450,7 +9420,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>-0.290021850881691</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="765">
@@ -9461,7 +9431,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.238848228289657</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="766">
@@ -9472,7 +9442,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.135885956610641</v>
+        <v>-0.192657171469523</v>
       </c>
     </row>
     <row r="767">
@@ -9483,7 +9453,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.326547837994405</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="768">
@@ -9494,7 +9464,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.167331746156435</v>
+        <v>-0.218678208911535</v>
       </c>
     </row>
     <row r="769">
@@ -9505,7 +9475,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.249860874679732</v>
+        <v>-0.299195203746955</v>
       </c>
     </row>
     <row r="770">
@@ -9516,7 +9486,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>0.0939362364001906</v>
+        <v>0.302439207210351</v>
       </c>
     </row>
     <row r="771">
@@ -9527,7 +9497,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.470183892749469</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="772">
@@ -9549,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.133354374107045</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="774">
@@ -9571,7 +9541,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.254228380917239</v>
+        <v>-0.189987846047261</v>
       </c>
     </row>
     <row r="776">
@@ -9582,7 +9552,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.542974589123902</v>
       </c>
     </row>
     <row r="777">
@@ -9593,7 +9563,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.330937327480967</v>
+        <v>0.0544566049529206</v>
       </c>
     </row>
     <row r="778">
@@ -9604,7 +9574,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.657032947340955</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="779">
@@ -9615,7 +9585,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.409470983805083</v>
       </c>
     </row>
     <row r="780">
@@ -9626,7 +9596,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>0.353835064365166</v>
+        <v>0.24193098897323</v>
       </c>
     </row>
     <row r="781">
@@ -9648,7 +9618,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.100436423787136</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="783">
@@ -9659,7 +9629,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-0.39881510667871</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="784">
@@ -9670,7 +9640,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.552065339963079</v>
+        <v>-0.167516886671899</v>
       </c>
     </row>
     <row r="785">
@@ -9681,7 +9651,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.193643177855034</v>
+        <v>-0.226198677299777</v>
       </c>
     </row>
     <row r="786">
@@ -9692,7 +9662,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.229540619525751</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="787">
@@ -9725,7 +9695,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.402012686702936</v>
+        <v>-0.209410819335585</v>
       </c>
     </row>
     <row r="790">
@@ -9736,7 +9706,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.255021326792482</v>
+        <v>-0.198662562304565</v>
       </c>
     </row>
     <row r="791">
@@ -9747,7 +9717,7 @@
         <v>16</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.216055747330148</v>
+        <v>-0.0517041193892112</v>
       </c>
     </row>
     <row r="792">
@@ -9758,7 +9728,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.297042896497858</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="793">
@@ -9769,7 +9739,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.314552937585446</v>
+        <v>-0.433283547551887</v>
       </c>
     </row>
     <row r="794">
@@ -9780,7 +9750,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.0779398388381916</v>
+        <v>0.0200351713730794</v>
       </c>
     </row>
     <row r="795">
@@ -9791,7 +9761,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>0.646394056904164</v>
+        <v>0.782864450915551</v>
       </c>
     </row>
     <row r="796">
@@ -9802,7 +9772,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.0444497595901503</v>
+        <v>-0.196491284394481</v>
       </c>
     </row>
     <row r="797">
@@ -9813,7 +9783,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.179211776057165</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="798">
@@ -9824,7 +9794,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.250611160425875</v>
       </c>
     </row>
     <row r="799">
@@ -9835,7 +9805,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.545385249907356</v>
+        <v>-0.460010968376358</v>
       </c>
     </row>
     <row r="800">
@@ -9846,7 +9816,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-0.434859993565378</v>
+        <v>-0.777693455246671</v>
       </c>
     </row>
     <row r="801">
@@ -9857,7 +9827,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>0.0445971468630026</v>
+        <v>-0.065208900167975</v>
       </c>
     </row>
     <row r="802">
@@ -9868,7 +9838,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.333634164488985</v>
+        <v>-0.462227005588448</v>
       </c>
     </row>
     <row r="803">
@@ -9890,7 +9860,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.298292379770884</v>
+        <v>-0.272598182270495</v>
       </c>
     </row>
     <row r="805">
@@ -9912,7 +9882,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.473128548288094</v>
+        <v>-0.191433946734536</v>
       </c>
     </row>
     <row r="807">
@@ -9923,7 +9893,7 @@
         <v>16</v>
       </c>
       <c r="C807" t="n">
-        <v>-0.0238698290048311</v>
+        <v>-0.148743548431295</v>
       </c>
     </row>
     <row r="808">
@@ -9934,7 +9904,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.475639428434562</v>
+        <v>-0.0248113263146801</v>
       </c>
     </row>
     <row r="809">
@@ -9945,7 +9915,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>-0.483257896979933</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="810">
@@ -9956,7 +9926,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.286999084041147</v>
+        <v>-0.444141699853612</v>
       </c>
     </row>
     <row r="811">
@@ -9967,7 +9937,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.514115898186924</v>
       </c>
     </row>
     <row r="812">
@@ -9978,7 +9948,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.27775116394502</v>
       </c>
     </row>
     <row r="813">
@@ -9989,7 +9959,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>0.462702686244144</v>
+        <v>0.0871338263149124</v>
       </c>
     </row>
     <row r="814">
@@ -10000,7 +9970,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.358941061900484</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="815">
@@ -10011,7 +9981,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>0.224570640411584</v>
+        <v>-0.205612953304831</v>
       </c>
     </row>
     <row r="816">
@@ -10022,7 +9992,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.662417840355259</v>
+        <v>-0.219800535079516</v>
       </c>
     </row>
     <row r="817">
@@ -10033,7 +10003,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-0.43532573750713</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="818">
@@ -10044,7 +10014,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>-0.135511654096124</v>
+        <v>-0.666907488705944</v>
       </c>
     </row>
     <row r="819">
@@ -10055,7 +10025,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.573803871692692</v>
+        <v>-0.385981530820177</v>
       </c>
     </row>
     <row r="820">
@@ -10077,7 +10047,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.144878981193559</v>
+        <v>-0.233226343841094</v>
       </c>
     </row>
     <row r="822">
@@ -10088,7 +10058,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.87835424190741</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="823">
@@ -10099,7 +10069,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.771744767229026</v>
+        <v>-0.948418658019119</v>
       </c>
     </row>
     <row r="824">
@@ -10110,7 +10080,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.296749830137181</v>
+        <v>-0.341290689050849</v>
       </c>
     </row>
     <row r="825">
@@ -10121,7 +10091,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.55157625736097</v>
+        <v>-0.808355718159354</v>
       </c>
     </row>
     <row r="826">
@@ -10154,7 +10124,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>0.0541037941166623</v>
+        <v>0.0554893530054849</v>
       </c>
     </row>
     <row r="829">
@@ -10165,7 +10135,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.256065490587425</v>
+        <v>-0.254610149061713</v>
       </c>
     </row>
     <row r="830">
@@ -10176,7 +10146,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.529923136587873</v>
+        <v>-0.412260172907167</v>
       </c>
     </row>
     <row r="831">
@@ -10187,7 +10157,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.198938481295567</v>
+        <v>-0.23031431171754</v>
       </c>
     </row>
     <row r="832">
@@ -10198,7 +10168,7 @@
         <v>16</v>
       </c>
       <c r="C832" t="n">
-        <v>-0.715096614824889</v>
+        <v>-0.893672134379094</v>
       </c>
     </row>
     <row r="833">
@@ -10209,7 +10179,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.50925206640906</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="834">
@@ -10220,7 +10190,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.6817901417308</v>
+        <v>-0.595317466610259</v>
       </c>
     </row>
     <row r="835">
@@ -10231,7 +10201,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>-0.0174874462074965</v>
+        <v>0.019201031836666</v>
       </c>
     </row>
     <row r="836">
@@ -10242,7 +10212,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.532867906033094</v>
+        <v>-0.290933715932865</v>
       </c>
     </row>
     <row r="837">
@@ -10253,7 +10223,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.232440234506472</v>
+        <v>-0.329048140906643</v>
       </c>
     </row>
     <row r="838">
@@ -10264,7 +10234,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.763169233051426</v>
+        <v>0.110790656336212</v>
       </c>
     </row>
     <row r="839">
@@ -10275,7 +10245,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.237947669280921</v>
       </c>
     </row>
     <row r="840">
@@ -10286,7 +10256,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.164406031603053</v>
       </c>
     </row>
     <row r="841">
@@ -10297,7 +10267,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.222997268247785</v>
+        <v>-0.472442501340391</v>
       </c>
     </row>
     <row r="842">
@@ -10319,7 +10289,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.380536574105669</v>
       </c>
     </row>
     <row r="844">
@@ -10330,7 +10300,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.320640605102289</v>
+        <v>-0.434660504720562</v>
       </c>
     </row>
     <row r="845">
@@ -10341,7 +10311,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.298771156141355</v>
+        <v>-0.334434961185876</v>
       </c>
     </row>
     <row r="846">
@@ -10352,7 +10322,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.334868518875859</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="847">
@@ -10363,7 +10333,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-1.06466123197933</v>
+        <v>-0.320008583602073</v>
       </c>
     </row>
     <row r="848">
@@ -10385,7 +10355,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.293797604635384</v>
+        <v>0.00957212563301046</v>
       </c>
     </row>
     <row r="850">
@@ -10396,7 +10366,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.44929516197226</v>
+        <v>-0.257103729319766</v>
       </c>
     </row>
     <row r="851">
@@ -10407,7 +10377,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.851423256726737</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="852">
@@ -10440,7 +10410,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.710204875677231</v>
+        <v>-0.291739342837058</v>
       </c>
     </row>
     <row r="855">
@@ -10451,7 +10421,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-0.482296463336132</v>
+        <v>0.0218687526153905</v>
       </c>
     </row>
     <row r="856">
@@ -10462,7 +10432,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.167066870326884</v>
       </c>
     </row>
     <row r="857">
@@ -10484,7 +10454,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.244006463852686</v>
+        <v>-0.0562113074513662</v>
       </c>
     </row>
     <row r="859">
@@ -10495,7 +10465,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>0.0954788720334938</v>
+        <v>0.34495051855043</v>
       </c>
     </row>
     <row r="860">
@@ -10506,7 +10476,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170992056343066</v>
       </c>
     </row>
     <row r="861">
@@ -10517,7 +10487,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.143451020773912</v>
+        <v>-0.151448049660972</v>
       </c>
     </row>
     <row r="862">
@@ -10528,7 +10498,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.783437349518069</v>
       </c>
     </row>
     <row r="863">
@@ -10539,7 +10509,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.251758456342263</v>
       </c>
     </row>
     <row r="864">
@@ -10550,7 +10520,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.21517526635472</v>
+        <v>-0.82656549442731</v>
       </c>
     </row>
     <row r="865">
@@ -10572,7 +10542,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>-0.189360972472704</v>
+        <v>-0.201893224228385</v>
       </c>
     </row>
     <row r="867">
@@ -10583,7 +10553,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.241006231022187</v>
+        <v>0.543690831460092</v>
       </c>
     </row>
     <row r="868">
@@ -10594,7 +10564,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.197343266856136</v>
+        <v>-0.744037370092716</v>
       </c>
     </row>
     <row r="869">
@@ -10605,7 +10575,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.383048440905361</v>
+        <v>-0.337390409572458</v>
       </c>
     </row>
     <row r="870">
@@ -10638,7 +10608,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.670567879185072</v>
+        <v>-0.418644835677034</v>
       </c>
     </row>
     <row r="873">
@@ -10660,7 +10630,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.334309773005058</v>
+        <v>-0.354508829555191</v>
       </c>
     </row>
     <row r="875">
@@ -10671,7 +10641,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.608154992497672</v>
+        <v>-0.222875853962306</v>
       </c>
     </row>
     <row r="876">
@@ -10682,7 +10652,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.0133422162925667</v>
+        <v>0.0393585654956687</v>
       </c>
     </row>
     <row r="877">
@@ -10704,7 +10674,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.328208265147273</v>
+        <v>-0.276090531114818</v>
       </c>
     </row>
     <row r="879">
@@ -10715,7 +10685,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-0.0367455379189388</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="880">
@@ -10726,7 +10696,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.633283124388374</v>
+        <v>-0.370938964630977</v>
       </c>
     </row>
     <row r="881">
@@ -10748,7 +10718,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.267596077638645</v>
+        <v>-0.369767191600213</v>
       </c>
     </row>
     <row r="883">
@@ -10759,7 +10729,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.248676072625564</v>
+        <v>0.108618950831118</v>
       </c>
     </row>
     <row r="884">
@@ -10770,7 +10740,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.168781114702813</v>
+        <v>-0.219965703774421</v>
       </c>
     </row>
     <row r="885">
@@ -10781,7 +10751,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.222398145237015</v>
+        <v>0.0610054358765855</v>
       </c>
     </row>
     <row r="886">
@@ -10803,7 +10773,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.717517190083474</v>
+        <v>-0.383597274529513</v>
       </c>
     </row>
     <row r="888">
@@ -10814,7 +10784,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>0.0676746568701243</v>
+        <v>-0.24813657935868</v>
       </c>
     </row>
     <row r="889">
@@ -10825,7 +10795,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.798100942837132</v>
+        <v>-0.409783442039128</v>
       </c>
     </row>
     <row r="890">
@@ -10836,7 +10806,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.178330938404078</v>
+        <v>-0.286730075883357</v>
       </c>
     </row>
     <row r="891">
@@ -10847,7 +10817,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.601458685590769</v>
+        <v>-0.337149133610356</v>
       </c>
     </row>
     <row r="892">
@@ -10858,7 +10828,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>0.37107316051056</v>
+        <v>0.338870915583482</v>
       </c>
     </row>
     <row r="893">
@@ -10869,7 +10839,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.260182914501134</v>
+        <v>-0.359870036541396</v>
       </c>
     </row>
     <row r="894">
@@ -10880,7 +10850,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.874837522811847</v>
+        <v>-0.186498910935536</v>
       </c>
     </row>
     <row r="895">
@@ -10891,7 +10861,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.334441722202684</v>
       </c>
     </row>
     <row r="896">
@@ -10902,7 +10872,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.225101807706991</v>
       </c>
     </row>
     <row r="897">
@@ -10913,7 +10883,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.256062871626979</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="898">
@@ -10924,7 +10894,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.248078342014872</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="899">
@@ -10946,7 +10916,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.173648299741806</v>
+        <v>-0.372603467763365</v>
       </c>
     </row>
     <row r="901">
@@ -10957,7 +10927,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.495917143000465</v>
+        <v>-0.756754432099997</v>
       </c>
     </row>
     <row r="902">
@@ -10968,7 +10938,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.497741663114509</v>
+        <v>-0.334644288223137</v>
       </c>
     </row>
     <row r="903">
@@ -10990,7 +10960,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-0.495803618854081</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="905">
@@ -11001,7 +10971,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.925280668918414</v>
+        <v>-0.268307075292118</v>
       </c>
     </row>
     <row r="906">
@@ -11012,7 +10982,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.284054383172604</v>
+        <v>-0.480822498005195</v>
       </c>
     </row>
     <row r="907">
@@ -11023,7 +10993,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.654465198389369</v>
+        <v>-0.384243997465779</v>
       </c>
     </row>
     <row r="908">
@@ -11034,7 +11004,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.40237930648185</v>
+        <v>-0.427595054302193</v>
       </c>
     </row>
     <row r="909">
@@ -11056,7 +11026,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.625117442043506</v>
+        <v>-0.393333837097107</v>
       </c>
     </row>
     <row r="911">
@@ -11078,7 +11048,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.238106515733822</v>
+        <v>-0.389825662392961</v>
       </c>
     </row>
     <row r="913">
@@ -11089,7 +11059,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.976453935331752</v>
+        <v>-0.234015953312506</v>
       </c>
     </row>
     <row r="914">
@@ -11100,7 +11070,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.429064216780078</v>
+        <v>-0.744106766456242</v>
       </c>
     </row>
     <row r="915">
@@ -11111,7 +11081,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.138016427455395</v>
+        <v>0.0527645447301396</v>
       </c>
     </row>
     <row r="916">
@@ -11122,7 +11092,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-0.472109199092148</v>
+        <v>-0.417402981247309</v>
       </c>
     </row>
     <row r="917">
@@ -11133,7 +11103,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.374275175628839</v>
+        <v>-0.29774348598041</v>
       </c>
     </row>
     <row r="918">
@@ -11144,7 +11114,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.202250027623728</v>
       </c>
     </row>
     <row r="919">
@@ -11155,7 +11125,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.614732159135112</v>
+        <v>-0.858686379340752</v>
       </c>
     </row>
     <row r="920">
@@ -11166,7 +11136,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.762987644672693</v>
+        <v>-0.490185702728919</v>
       </c>
     </row>
     <row r="921">
@@ -11177,7 +11147,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.559209889716528</v>
+        <v>-0.511267445606289</v>
       </c>
     </row>
     <row r="922">
@@ -11188,7 +11158,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.230608499205951</v>
+        <v>-0.568806444437253</v>
       </c>
     </row>
     <row r="923">
@@ -11199,7 +11169,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.882470846301632</v>
+        <v>-0.493594892709725</v>
       </c>
     </row>
     <row r="924">
@@ -11210,7 +11180,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.45079773739368</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="925">
@@ -11221,7 +11191,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.244526346613352</v>
+        <v>0.0563299495451588</v>
       </c>
     </row>
     <row r="926">
@@ -11232,7 +11202,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.591899280469242</v>
       </c>
     </row>
     <row r="927">
@@ -11243,7 +11213,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.166494287708448</v>
       </c>
     </row>
     <row r="928">
@@ -11254,7 +11224,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.48025264537586</v>
+        <v>-0.167958764794704</v>
       </c>
     </row>
     <row r="929">
@@ -11265,7 +11235,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.445400622225029</v>
+        <v>-0.13553712452719</v>
       </c>
     </row>
     <row r="930">
@@ -11276,7 +11246,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>0.303088872523663</v>
+        <v>-0.167541312076247</v>
       </c>
     </row>
     <row r="931">
@@ -11287,7 +11257,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.439142455324134</v>
+        <v>-0.30340686169784</v>
       </c>
     </row>
     <row r="932">
@@ -11298,7 +11268,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.672453575843497</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="933">
@@ -11309,7 +11279,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.208355385447285</v>
+        <v>-0.22584211763742</v>
       </c>
     </row>
     <row r="934">
@@ -11320,7 +11290,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>-0.316959149904888</v>
+        <v>-0.514794868333774</v>
       </c>
     </row>
     <row r="935">
@@ -11331,7 +11301,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.357891124394857</v>
+        <v>-0.540185777575176</v>
       </c>
     </row>
     <row r="936">
@@ -11342,7 +11312,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.746252142591508</v>
+        <v>-0.867897227216611</v>
       </c>
     </row>
     <row r="937">
@@ -11353,7 +11323,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.171756057975433</v>
+        <v>-1.32810852495051</v>
       </c>
     </row>
     <row r="938">
@@ -11364,7 +11334,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.333708976210193</v>
+        <v>-1.05580359949301</v>
       </c>
     </row>
     <row r="939">
@@ -11386,7 +11356,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>0.0205036774361619</v>
+        <v>-0.370813434741289</v>
       </c>
     </row>
     <row r="941">
@@ -11408,7 +11378,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-1.01925172050989</v>
+        <v>-0.240718407686187</v>
       </c>
     </row>
     <row r="943">
@@ -11419,7 +11389,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.27591849041497</v>
+        <v>-0.258216839025648</v>
       </c>
     </row>
     <row r="944">
@@ -11441,7 +11411,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>0.401071067953517</v>
+        <v>0.251218856602648</v>
       </c>
     </row>
     <row r="946">
@@ -11452,7 +11422,7 @@
         <v>16</v>
       </c>
       <c r="C946" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.162821452030306</v>
       </c>
     </row>
     <row r="947">
@@ -11463,7 +11433,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-1.04324620579337</v>
+        <v>-0.199237036578808</v>
       </c>
     </row>
     <row r="948">
@@ -11474,7 +11444,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.188617765439881</v>
+        <v>-0.237328139665895</v>
       </c>
     </row>
     <row r="949">
@@ -11496,7 +11466,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.436896527589796</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="951">
@@ -11507,7 +11477,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>-0.68493377640685</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="952">
@@ -11540,7 +11510,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.599925902338646</v>
+        <v>-0.646060677716117</v>
       </c>
     </row>
     <row r="955">
@@ -11551,7 +11521,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.122345492478721</v>
+        <v>-0.307403933099309</v>
       </c>
     </row>
     <row r="956">
@@ -11562,7 +11532,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.50488301786556</v>
+        <v>-0.687735305303283</v>
       </c>
     </row>
     <row r="957">
@@ -11573,7 +11543,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.205421238956756</v>
+        <v>-0.311223187032809</v>
       </c>
     </row>
     <row r="958">
@@ -11595,7 +11565,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.426566921878301</v>
+        <v>-0.560762313520515</v>
       </c>
     </row>
     <row r="960">
@@ -11606,7 +11576,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>0.0907488904457109</v>
+        <v>0.107460950241918</v>
       </c>
     </row>
     <row r="961">
@@ -11617,7 +11587,7 @@
         <v>16</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.225647027919461</v>
+        <v>-0.272708633798401</v>
       </c>
     </row>
     <row r="962">
@@ -11628,7 +11598,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.440949527700622</v>
+        <v>-0.548924437202803</v>
       </c>
     </row>
     <row r="963">
@@ -11639,7 +11609,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.0933629879426043</v>
+        <v>-0.430603748308008</v>
       </c>
     </row>
     <row r="964">
@@ -11650,7 +11620,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.427070796541515</v>
       </c>
     </row>
     <row r="965">
@@ -11661,7 +11631,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.482079044508119</v>
+        <v>-0.397139608329311</v>
       </c>
     </row>
     <row r="966">
@@ -11672,7 +11642,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.653840112825979</v>
+        <v>-1.95525128713918</v>
       </c>
     </row>
     <row r="967">
@@ -11694,7 +11664,7 @@
         <v>16</v>
       </c>
       <c r="C968" t="n">
-        <v>0.438463705796039</v>
+        <v>0.451894060042339</v>
       </c>
     </row>
     <row r="969">
@@ -11727,7 +11697,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.562266764120805</v>
+        <v>-0.185671920538886</v>
       </c>
     </row>
     <row r="972">
@@ -11738,7 +11708,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.190502054155393</v>
       </c>
     </row>
     <row r="973">
@@ -11749,7 +11719,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.511581953635774</v>
+        <v>-0.629251597133031</v>
       </c>
     </row>
     <row r="974">
@@ -11760,7 +11730,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.170458599318642</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="975">
@@ -11771,7 +11741,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.775413395593727</v>
+        <v>-0.648704726227834</v>
       </c>
     </row>
     <row r="976">
@@ -11782,7 +11752,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.243721073927015</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="977">
@@ -11793,7 +11763,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.230149406082981</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="978">
@@ -11804,7 +11774,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.218547163311699</v>
       </c>
     </row>
     <row r="979">
@@ -11815,7 +11785,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.257923819469332</v>
       </c>
     </row>
     <row r="980">
@@ -11837,7 +11807,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>0.356899426977928</v>
+        <v>-0.218909705925625</v>
       </c>
     </row>
     <row r="982">
@@ -11848,7 +11818,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.182947099054262</v>
+        <v>-0.472506061455722</v>
       </c>
     </row>
     <row r="983">
@@ -11859,7 +11829,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.343846914362898</v>
+        <v>-0.233353981982489</v>
       </c>
     </row>
     <row r="984">
@@ -11881,7 +11851,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.614238260687024</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="986">
@@ -11892,7 +11862,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-0.0416343472283331</v>
+        <v>0.0086252353800288</v>
       </c>
     </row>
     <row r="987">
@@ -11903,7 +11873,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.181455454524317</v>
+        <v>-0.224065976917421</v>
       </c>
     </row>
     <row r="988">
@@ -11914,7 +11884,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.295561974991151</v>
+        <v>-0.539381097312355</v>
       </c>
     </row>
     <row r="989">
@@ -11925,7 +11895,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.270637862341192</v>
       </c>
     </row>
     <row r="990">
@@ -11936,7 +11906,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.235146385725918</v>
+        <v>-0.248485057149131</v>
       </c>
     </row>
     <row r="991">
@@ -11947,7 +11917,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.48784468826619</v>
+        <v>-0.0283178409838307</v>
       </c>
     </row>
     <row r="992">
@@ -11958,7 +11928,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.289675623339206</v>
+        <v>-0.353872745306104</v>
       </c>
     </row>
     <row r="993">
@@ -11969,7 +11939,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.384625466152106</v>
+        <v>-0.453577648662573</v>
       </c>
     </row>
     <row r="994">
@@ -11980,7 +11950,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.435444837994994</v>
+        <v>-0.385552464088117</v>
       </c>
     </row>
     <row r="995">
@@ -12002,7 +11972,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.215820351613486</v>
+        <v>-0.335334257658579</v>
       </c>
     </row>
     <row r="997">
@@ -12013,7 +11983,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.247195247964169</v>
+        <v>-0.345746150580405</v>
       </c>
     </row>
     <row r="998">
@@ -12024,7 +11994,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.172265001852649</v>
+        <v>-0.143785857465426</v>
       </c>
     </row>
     <row r="999">
@@ -12046,7 +12016,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.324249473434391</v>
       </c>
     </row>
     <row r="1001">
@@ -12057,7 +12027,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.266724563874884</v>
+        <v>-0.388138485134308</v>
       </c>
     </row>
     <row r="1002">
@@ -12068,7 +12038,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.180819899065794</v>
       </c>
     </row>
     <row r="1003">
@@ -12079,7 +12049,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.365666511630034</v>
+        <v>-0.29257574015708</v>
       </c>
     </row>
     <row r="1004">
@@ -12101,7 +12071,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.576845614246752</v>
+        <v>-0.362372845473593</v>
       </c>
     </row>
     <row r="1006">
@@ -12112,7 +12082,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.266844542809171</v>
+        <v>-0.735157354820345</v>
       </c>
     </row>
     <row r="1007">
@@ -12123,7 +12093,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.819362840586377</v>
+        <v>-1.37629625050245</v>
       </c>
     </row>
     <row r="1008">
@@ -12134,7 +12104,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.808061915548405</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1009">
@@ -12145,7 +12115,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.230275883810372</v>
+        <v>-0.286130632764241</v>
       </c>
     </row>
     <row r="1010">
@@ -12167,7 +12137,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.885515616766941</v>
+        <v>-0.778253125067304</v>
       </c>
     </row>
     <row r="1012">
@@ -12178,7 +12148,7 @@
         <v>16</v>
       </c>
       <c r="C1012" t="n">
-        <v>-0.55457001314338</v>
+        <v>-0.399921042211556</v>
       </c>
     </row>
     <row r="1013">
@@ -12189,7 +12159,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>0.432186631489853</v>
+        <v>0.395058021647358</v>
       </c>
     </row>
     <row r="1014">
@@ -12200,7 +12170,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.36340981094802</v>
+        <v>-0.328945141152911</v>
       </c>
     </row>
     <row r="1015">
@@ -12211,7 +12181,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.214730616214809</v>
+        <v>-0.292303997349059</v>
       </c>
     </row>
     <row r="1016">
@@ -12222,7 +12192,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.250377997156367</v>
+        <v>-0.602024920067674</v>
       </c>
     </row>
     <row r="1017">
@@ -12233,7 +12203,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-0.357986690943988</v>
+        <v>-0.324196609642907</v>
       </c>
     </row>
     <row r="1018">
@@ -12244,7 +12214,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.269712944178409</v>
+        <v>-0.186347054915338</v>
       </c>
     </row>
     <row r="1019">
@@ -12255,7 +12225,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>-0.220648204769623</v>
+        <v>-0.308951604117694</v>
       </c>
     </row>
     <row r="1020">
@@ -12277,7 +12247,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.187463562125685</v>
+        <v>-0.202789327591513</v>
       </c>
     </row>
     <row r="1022">
@@ -12288,7 +12258,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.381711317291511</v>
+        <v>0.258889504897237</v>
       </c>
     </row>
     <row r="1023">
@@ -12299,7 +12269,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.223483050326757</v>
       </c>
     </row>
     <row r="1024">
@@ -12310,7 +12280,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.130481556757179</v>
+        <v>-0.241045942813642</v>
       </c>
     </row>
     <row r="1025">
@@ -12321,7 +12291,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.315845683039112</v>
+        <v>-0.469711671104106</v>
       </c>
     </row>
     <row r="1026">
@@ -12332,7 +12302,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.333624446810828</v>
+        <v>-0.135027545229628</v>
       </c>
     </row>
     <row r="1027">
@@ -12343,7 +12313,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.461687225894143</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1028">
@@ -12354,7 +12324,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>0.0921702160059389</v>
+        <v>-0.547255041817543</v>
       </c>
     </row>
     <row r="1029">
@@ -12365,7 +12335,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.162637965383781</v>
       </c>
     </row>
     <row r="1030">
@@ -12387,7 +12357,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.274475565186008</v>
+        <v>-0.176099414007083</v>
       </c>
     </row>
     <row r="1032">
@@ -12398,7 +12368,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.550398830229103</v>
+        <v>-0.326224698960848</v>
       </c>
     </row>
     <row r="1033">
@@ -12409,7 +12379,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.118120121979452</v>
+        <v>-0.153792725426079</v>
       </c>
     </row>
     <row r="1034">
@@ -12431,7 +12401,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.201423357104777</v>
+        <v>-0.206254483875632</v>
       </c>
     </row>
     <row r="1036">
@@ -12442,7 +12412,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.443071326674377</v>
+        <v>-0.40532090578358</v>
       </c>
     </row>
     <row r="1037">
@@ -12453,7 +12423,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.51161550261789</v>
+        <v>-0.776642611556164</v>
       </c>
     </row>
     <row r="1038">
@@ -12475,7 +12445,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.360430721882648</v>
+        <v>-0.383172761519906</v>
       </c>
     </row>
     <row r="1040">
@@ -12486,7 +12456,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.383290097996438</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1041">
@@ -12497,7 +12467,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.517258264280797</v>
+        <v>-0.57359055255921</v>
       </c>
     </row>
     <row r="1042">
@@ -12508,7 +12478,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.303088889048812</v>
+        <v>-0.426595334826565</v>
       </c>
     </row>
     <row r="1043">
@@ -12530,7 +12500,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.2759558381972</v>
+        <v>-0.48357302045236</v>
       </c>
     </row>
     <row r="1045">
@@ -12563,7 +12533,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.222142534298396</v>
+        <v>-0.231176992420226</v>
       </c>
     </row>
     <row r="1048">
@@ -12574,7 +12544,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.223318631946734</v>
+        <v>-0.249412240766043</v>
       </c>
     </row>
     <row r="1049">
@@ -12585,7 +12555,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.293095406210997</v>
+        <v>-0.360757364842512</v>
       </c>
     </row>
     <row r="1050">
@@ -12607,7 +12577,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.507281075648232</v>
       </c>
     </row>
     <row r="1052">
@@ -12629,7 +12599,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.468545304369946</v>
+        <v>-0.467842774417953</v>
       </c>
     </row>
     <row r="1054">
@@ -12651,7 +12621,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.219573028268066</v>
       </c>
     </row>
     <row r="1056">
@@ -12662,7 +12632,7 @@
         <v>16</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.0311062877747532</v>
+        <v>-0.260449312361214</v>
       </c>
     </row>
     <row r="1057">
@@ -12673,7 +12643,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.465716357593706</v>
+        <v>-0.28376644940445</v>
       </c>
     </row>
     <row r="1058">
@@ -12684,7 +12654,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.37024839951003</v>
+        <v>-0.265709047626504</v>
       </c>
     </row>
     <row r="1059">
@@ -12695,7 +12665,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>-0.776624993889597</v>
+        <v>-0.689124966258307</v>
       </c>
     </row>
     <row r="1060">
@@ -12706,7 +12676,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.343376915413005</v>
+        <v>-0.682393362355546</v>
       </c>
     </row>
     <row r="1061">
@@ -12717,7 +12687,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.231107686053495</v>
+        <v>-0.925127389473793</v>
       </c>
     </row>
     <row r="1062">
@@ -12728,7 +12698,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.378458673051902</v>
+        <v>-0.467134608113091</v>
       </c>
     </row>
     <row r="1063">
@@ -12739,7 +12709,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.49048554728959</v>
+        <v>-0.54062617791843</v>
       </c>
     </row>
     <row r="1064">
@@ -12750,7 +12720,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.235957144227925</v>
+        <v>-0.462592609256837</v>
       </c>
     </row>
     <row r="1065">
@@ -12761,7 +12731,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.174013959488553</v>
+        <v>-0.204260186484199</v>
       </c>
     </row>
     <row r="1066">
@@ -12772,7 +12742,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.711054451850407</v>
+        <v>-0.369452806641087</v>
       </c>
     </row>
     <row r="1067">
@@ -12783,7 +12753,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.128262930730993</v>
+        <v>-0.4645782205936</v>
       </c>
     </row>
     <row r="1068">
@@ -12794,7 +12764,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-1.08933656239229</v>
+        <v>-0.173513942058552</v>
       </c>
     </row>
     <row r="1069">
@@ -12805,7 +12775,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>0.0562689108100436</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1070">
@@ -12816,7 +12786,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.573510216286459</v>
+        <v>-0.753799537350454</v>
       </c>
     </row>
     <row r="1071">
@@ -12827,7 +12797,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.202748892449472</v>
+        <v>-0.517993381552358</v>
       </c>
     </row>
     <row r="1072">
@@ -12838,7 +12808,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.424871942035384</v>
+        <v>-0.0254988763496313</v>
       </c>
     </row>
     <row r="1073">
@@ -12849,7 +12819,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.534565697260751</v>
+        <v>-0.631458498892351</v>
       </c>
     </row>
     <row r="1074">
@@ -12860,7 +12830,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.380927309348396</v>
+        <v>-0.433691436271593</v>
       </c>
     </row>
     <row r="1075">
@@ -12871,7 +12841,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.218626098408372</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1076">
@@ -12882,7 +12852,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.784144164599228</v>
       </c>
     </row>
     <row r="1077">
@@ -12893,7 +12863,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.547907483615685</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1078">
@@ -12904,7 +12874,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.156141184027623</v>
+        <v>-0.147978818379275</v>
       </c>
     </row>
     <row r="1079">
@@ -12915,7 +12885,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.567113219308581</v>
+        <v>-0.388628105233501</v>
       </c>
     </row>
     <row r="1080">
@@ -12926,7 +12896,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.424605006138142</v>
+        <v>-0.408917066572368</v>
       </c>
     </row>
     <row r="1081">
@@ -12937,7 +12907,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.179867586225635</v>
       </c>
     </row>
     <row r="1082">
@@ -12948,7 +12918,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>0.134992777978332</v>
+        <v>-0.338262571969058</v>
       </c>
     </row>
     <row r="1083">
@@ -12959,7 +12929,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.234563862648732</v>
+        <v>-0.215369401893884</v>
       </c>
     </row>
     <row r="1084">
@@ -12970,7 +12940,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.39484464469449</v>
       </c>
     </row>
     <row r="1085">
@@ -12981,7 +12951,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.0292642246339201</v>
+        <v>-0.05301644328891</v>
       </c>
     </row>
     <row r="1086">
@@ -13003,7 +12973,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.25666192292763</v>
+        <v>-0.500276970234895</v>
       </c>
     </row>
     <row r="1088">
@@ -13014,7 +12984,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.580196464220135</v>
+        <v>-0.740739602929115</v>
       </c>
     </row>
     <row r="1089">
@@ -13025,7 +12995,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.353839387431437</v>
+        <v>-0.20816178359715</v>
       </c>
     </row>
     <row r="1090">
@@ -13058,7 +13028,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.25667922008513</v>
+        <v>-1.05510815341404</v>
       </c>
     </row>
     <row r="1093">
@@ -13069,7 +13039,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.514624820073774</v>
+        <v>-0.311691520920719</v>
       </c>
     </row>
     <row r="1094">
@@ -13080,7 +13050,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.549775801107659</v>
+        <v>-0.775199986113568</v>
       </c>
     </row>
     <row r="1095">
@@ -13091,7 +13061,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-1.2133903581346</v>
+        <v>-0.339595923984677</v>
       </c>
     </row>
     <row r="1096">
@@ -13102,7 +13072,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.272177714045923</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1097">
@@ -13113,7 +13083,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.669774066092359</v>
+        <v>-0.68662684921868</v>
       </c>
     </row>
     <row r="1098">
@@ -13124,7 +13094,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.628022698593012</v>
+        <v>-0.231672355348797</v>
       </c>
     </row>
     <row r="1099">
@@ -13135,7 +13105,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.18989737274523</v>
       </c>
     </row>
     <row r="1100">
@@ -13146,7 +13116,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.277953709793191</v>
+        <v>-0.205864645144145</v>
       </c>
     </row>
     <row r="1101">
@@ -13157,7 +13127,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.625745559688867</v>
       </c>
     </row>
     <row r="1102">
@@ -13168,7 +13138,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.340144880977988</v>
+        <v>-0.233741702221803</v>
       </c>
     </row>
     <row r="1103">
@@ -13179,7 +13149,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.512790400447506</v>
+        <v>-0.673034564481648</v>
       </c>
     </row>
     <row r="1104">
@@ -13201,7 +13171,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.687094870724245</v>
+        <v>-0.663021649295733</v>
       </c>
     </row>
     <row r="1106">
@@ -13223,7 +13193,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.424451223916083</v>
+        <v>-0.272605336069164</v>
       </c>
     </row>
     <row r="1108">
@@ -13234,7 +13204,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.497214703097806</v>
+        <v>-0.193144682631661</v>
       </c>
     </row>
     <row r="1109">
@@ -13245,7 +13215,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.44598881752531</v>
+        <v>-0.730033355366561</v>
       </c>
     </row>
     <row r="1110">
@@ -13256,7 +13226,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.585993033152114</v>
+        <v>-0.640730520292938</v>
       </c>
     </row>
     <row r="1111">
@@ -13289,7 +13259,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.721867114260457</v>
+        <v>-0.801369763499989</v>
       </c>
     </row>
     <row r="1114">
@@ -13300,7 +13270,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.397345713538525</v>
+        <v>0.577824830668596</v>
       </c>
     </row>
     <row r="1115">
@@ -13311,7 +13281,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.558428771260005</v>
+        <v>-0.698265978247895</v>
       </c>
     </row>
     <row r="1116">
@@ -13322,7 +13292,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>0.0457704797150428</v>
+        <v>-0.115553928669491</v>
       </c>
     </row>
     <row r="1117">
@@ -13333,7 +13303,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.546914465592213</v>
+        <v>-0.113705603399302</v>
       </c>
     </row>
     <row r="1118">
@@ -13355,7 +13325,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.229225511841412</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1120">
@@ -13366,7 +13336,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.767997132654012</v>
       </c>
     </row>
     <row r="1121">
@@ -13377,7 +13347,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.622877877914178</v>
+        <v>-0.579747011436213</v>
       </c>
     </row>
     <row r="1122">
@@ -13388,7 +13358,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.474557202789884</v>
+        <v>-0.0134639029307819</v>
       </c>
     </row>
     <row r="1123">
@@ -13399,7 +13369,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.502811166831353</v>
+        <v>-0.110613710671331</v>
       </c>
     </row>
     <row r="1124">
@@ -13410,7 +13380,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.665348341738294</v>
+        <v>-0.31754682543677</v>
       </c>
     </row>
     <row r="1125">
@@ -13421,7 +13391,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>0.143008677253537</v>
+        <v>-0.662383029916788</v>
       </c>
     </row>
     <row r="1126">
@@ -13454,7 +13424,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.248683373313883</v>
+        <v>-0.229383306238878</v>
       </c>
     </row>
     <row r="1129">
@@ -13465,7 +13435,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.391888488493447</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1130">
@@ -13476,7 +13446,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.566373794346371</v>
+        <v>-0.581626083106549</v>
       </c>
     </row>
     <row r="1131">
@@ -13487,7 +13457,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.287745467658705</v>
+        <v>-0.287552288352713</v>
       </c>
     </row>
     <row r="1132">
@@ -13498,7 +13468,7 @@
         <v>16</v>
       </c>
       <c r="C1132" t="n">
-        <v>-0.246990736298842</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1133">
@@ -13509,7 +13479,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.363594524960339</v>
+        <v>-0.40977115376066</v>
       </c>
     </row>
     <row r="1134">
@@ -13531,7 +13501,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-1.40390099114609</v>
+        <v>-0.39708719856245</v>
       </c>
     </row>
     <row r="1136">
@@ -13542,7 +13512,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.52101760591599</v>
+        <v>-0.464148025625243</v>
       </c>
     </row>
     <row r="1137">
@@ -13553,7 +13523,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.832907235299742</v>
+        <v>-0.386366671690591</v>
       </c>
     </row>
     <row r="1138">
@@ -13564,7 +13534,7 @@
         <v>16</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.249148307196778</v>
       </c>
     </row>
     <row r="1139">
@@ -13575,7 +13545,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.227723615293045</v>
+        <v>-0.195666295932106</v>
       </c>
     </row>
     <row r="1140">
@@ -13586,7 +13556,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.374029206700586</v>
       </c>
     </row>
     <row r="1141">
@@ -13597,7 +13567,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.175773268720594</v>
+        <v>-0.173359395017013</v>
       </c>
     </row>
     <row r="1142">
@@ -13608,7 +13578,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.302231365522581</v>
+        <v>-0.282208709088085</v>
       </c>
     </row>
     <row r="1143">
@@ -13619,7 +13589,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.80408307450216</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1144">
@@ -13630,7 +13600,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.33613999348924</v>
       </c>
     </row>
     <row r="1145">
@@ -13652,7 +13622,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.445004496216006</v>
+        <v>-0.409351297558338</v>
       </c>
     </row>
     <row r="1147">
@@ -13663,7 +13633,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.330122354948107</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1148">
@@ -13685,7 +13655,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.610108471097535</v>
+        <v>-0.57403801812541</v>
       </c>
     </row>
     <row r="1150">
@@ -13696,7 +13666,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.6118379838723</v>
+        <v>-0.42638849591356</v>
       </c>
     </row>
     <row r="1151">
@@ -13707,7 +13677,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.219644564517811</v>
+        <v>-0.380584966635678</v>
       </c>
     </row>
     <row r="1152">
@@ -13718,7 +13688,7 @@
         <v>16</v>
       </c>
       <c r="C1152" t="n">
-        <v>-0.182120232205858</v>
+        <v>-0.423642921828979</v>
       </c>
     </row>
     <row r="1153">
@@ -13729,7 +13699,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>-0.521548534205362</v>
+        <v>-0.74326577740192</v>
       </c>
     </row>
     <row r="1154">
@@ -13751,7 +13721,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.26895222506119</v>
       </c>
     </row>
     <row r="1156">
@@ -13773,7 +13743,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-0.705244018653219</v>
+        <v>-0.416214505941465</v>
       </c>
     </row>
     <row r="1158">
@@ -13784,7 +13754,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.195934293313545</v>
+        <v>-0.193337794701666</v>
       </c>
     </row>
     <row r="1159">
@@ -13795,7 +13765,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.564649419241334</v>
+        <v>-0.686584876020665</v>
       </c>
     </row>
     <row r="1160">
@@ -13817,7 +13787,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.155832451599091</v>
+        <v>-0.189778147020417</v>
       </c>
     </row>
     <row r="1162">
@@ -13828,7 +13798,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.397095654257413</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1163">
@@ -13839,7 +13809,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.0183661014450194</v>
+        <v>-0.0618934408977656</v>
       </c>
     </row>
     <row r="1164">
@@ -13850,7 +13820,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0931832743213012</v>
       </c>
     </row>
     <row r="1165">
@@ -13861,7 +13831,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.227762656051721</v>
+        <v>-0.171380031750045</v>
       </c>
     </row>
     <row r="1166">
@@ -13883,7 +13853,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.277715523728167</v>
+        <v>-0.329904276215325</v>
       </c>
     </row>
     <row r="1168">
@@ -13894,7 +13864,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.33509475418115</v>
+        <v>-0.494519376378265</v>
       </c>
     </row>
     <row r="1169">
@@ -13905,7 +13875,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.54036738355529</v>
+        <v>-0.398699335559982</v>
       </c>
     </row>
     <row r="1170">
@@ -13916,7 +13886,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>0.0941670262308764</v>
+        <v>-0.228891210645614</v>
       </c>
     </row>
     <row r="1171">
@@ -13927,7 +13897,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.56641462858404</v>
+        <v>-0.446333401893054</v>
       </c>
     </row>
     <row r="1172">
@@ -13938,7 +13908,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.228773857559508</v>
+        <v>-0.261560663980333</v>
       </c>
     </row>
     <row r="1173">
@@ -13949,7 +13919,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.175672233215768</v>
       </c>
     </row>
     <row r="1174">
@@ -13960,7 +13930,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.464746462981197</v>
+        <v>-0.554715844966818</v>
       </c>
     </row>
     <row r="1175">
@@ -13993,7 +13963,7 @@
         <v>16</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.229837893796935</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1178">
@@ -14015,7 +13985,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.906989307397167</v>
+        <v>-0.476921233067869</v>
       </c>
     </row>
     <row r="1180">
@@ -14026,7 +13996,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.670958320134915</v>
+        <v>-0.683827423692658</v>
       </c>
     </row>
     <row r="1181">
@@ -14037,7 +14007,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.180218365373359</v>
+        <v>-0.185388686052357</v>
       </c>
     </row>
     <row r="1182">
@@ -14048,7 +14018,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.746560813070885</v>
+        <v>-0.75572292566877</v>
       </c>
     </row>
     <row r="1183">
@@ -14059,7 +14029,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.321880613736723</v>
+        <v>0.0230702927787734</v>
       </c>
     </row>
     <row r="1184">
@@ -14070,7 +14040,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.657121945585131</v>
+        <v>-0.730745110880805</v>
       </c>
     </row>
     <row r="1185">
@@ -14081,7 +14051,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.36202350069289</v>
+        <v>-0.241412103965261</v>
       </c>
     </row>
     <row r="1186">
@@ -14092,7 +14062,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>0.240933994772538</v>
+        <v>0.100266234828484</v>
       </c>
     </row>
     <row r="1187">
@@ -14114,7 +14084,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.179754208389946</v>
       </c>
     </row>
     <row r="1189">
@@ -14125,7 +14095,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.201137305584111</v>
+        <v>-0.471781269204345</v>
       </c>
     </row>
     <row r="1190">
@@ -14136,7 +14106,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>0.425386854980298</v>
+        <v>-0.746958808836802</v>
       </c>
     </row>
     <row r="1191">
@@ -14147,7 +14117,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.182994024158311</v>
+        <v>-0.166836213215052</v>
       </c>
     </row>
     <row r="1192">
@@ -14158,7 +14128,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.351492448521115</v>
+        <v>-0.147197170591112</v>
       </c>
     </row>
     <row r="1193">
@@ -14169,7 +14139,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.448267693793841</v>
+        <v>-0.650806246983428</v>
       </c>
     </row>
     <row r="1194">
@@ -14180,7 +14150,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.497242774854996</v>
+        <v>-0.446796994938199</v>
       </c>
     </row>
     <row r="1195">
@@ -14191,7 +14161,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.705861415736935</v>
+        <v>-0.42736585361645</v>
       </c>
     </row>
     <row r="1196">
@@ -14202,7 +14172,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.407641348314937</v>
+        <v>-0.513458120648749</v>
       </c>
     </row>
     <row r="1197">
@@ -14213,7 +14183,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.219884006709991</v>
+        <v>-0.530460989367148</v>
       </c>
     </row>
     <row r="1198">
@@ -14235,7 +14205,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.347872591468612</v>
+        <v>-1.47484311008556</v>
       </c>
     </row>
     <row r="1200">
@@ -14246,7 +14216,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.528120438154892</v>
+        <v>-0.19821859053766</v>
       </c>
     </row>
     <row r="1201">
@@ -14336,7 +14306,7 @@
         <v>13.69</v>
       </c>
       <c r="E4" t="n">
-        <v>1.97724385807174</v>
+        <v>2.73553556802975</v>
       </c>
     </row>
     <row r="5">
@@ -14353,7 +14323,7 @@
         <v>10.45</v>
       </c>
       <c r="E5" t="n">
-        <v>4.18846153846154</v>
+        <v>4.16877278036395</v>
       </c>
     </row>
     <row r="6">
@@ -14387,7 +14357,7 @@
         <v>13.79</v>
       </c>
       <c r="E7" t="n">
-        <v>3.93153846153846</v>
+        <v>3.37142394939654</v>
       </c>
     </row>
     <row r="8">
@@ -14455,7 +14425,7 @@
         <v>-0.74</v>
       </c>
       <c r="E11" t="n">
-        <v>5.04923076923077</v>
+        <v>4.68240943537768</v>
       </c>
     </row>
     <row r="12">
@@ -14472,7 +14442,7 @@
         <v>-1.86</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8573423761133</v>
+        <v>19.6177839891524</v>
       </c>
     </row>
     <row r="13">
@@ -14557,7 +14527,7 @@
         <v>1757.71</v>
       </c>
       <c r="E17" t="n">
-        <v>-18.9172648322528</v>
+        <v>-356.82</v>
       </c>
     </row>
     <row r="18">
@@ -14591,7 +14561,7 @@
         <v>274.62</v>
       </c>
       <c r="E19" t="n">
-        <v>-430.569058994245</v>
+        <v>-242.736153846154</v>
       </c>
     </row>
     <row r="20">
@@ -14608,7 +14578,7 @@
         <v>545.54</v>
       </c>
       <c r="E20" t="n">
-        <v>797.521176704898</v>
+        <v>-263.576153846154</v>
       </c>
     </row>
     <row r="21">
@@ -14727,7 +14697,7 @@
         <v>-1385.12</v>
       </c>
       <c r="E27" t="n">
-        <v>-372.94233026521</v>
+        <v>-115.063846153846</v>
       </c>
     </row>
     <row r="28">
@@ -14761,7 +14731,7 @@
         <v>-1268.92</v>
       </c>
       <c r="E29" t="n">
-        <v>-1621.78733980043</v>
+        <v>-124.002307692308</v>
       </c>
     </row>
     <row r="30">
@@ -14880,7 +14850,7 @@
         <v>-171.76</v>
       </c>
       <c r="E36" t="n">
-        <v>2373.07455785934</v>
+        <v>48.5523076923077</v>
       </c>
     </row>
     <row r="37">
@@ -15016,7 +14986,7 @@
         <v>1.706</v>
       </c>
       <c r="E44" t="n">
-        <v>2.11615820771033</v>
+        <v>2.05656745946646</v>
       </c>
     </row>
     <row r="45">
@@ -15033,7 +15003,7 @@
         <v>4.218</v>
       </c>
       <c r="E45" t="n">
-        <v>1.52785505950969</v>
+        <v>1.37845314565278</v>
       </c>
     </row>
     <row r="46">
@@ -15050,7 +15020,7 @@
         <v>1.578</v>
       </c>
       <c r="E46" t="n">
-        <v>0.795739778166774</v>
+        <v>0.793437724386766</v>
       </c>
     </row>
     <row r="47">
@@ -15067,7 +15037,7 @@
         <v>3.683</v>
       </c>
       <c r="E47" t="n">
-        <v>2.18843795176181</v>
+        <v>2.45217606867959</v>
       </c>
     </row>
     <row r="48">
@@ -15084,7 +15054,7 @@
         <v>2.983</v>
       </c>
       <c r="E48" t="n">
-        <v>3.63917398424385</v>
+        <v>4.86111054398436</v>
       </c>
     </row>
     <row r="49">
@@ -15101,7 +15071,7 @@
         <v>2.44</v>
       </c>
       <c r="E49" t="n">
-        <v>1.15110662138356</v>
+        <v>1.25570669160531</v>
       </c>
     </row>
     <row r="50">
@@ -15118,7 +15088,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E50" t="n">
-        <v>1.19187327335648</v>
+        <v>1.27247044659088</v>
       </c>
     </row>
     <row r="51">
@@ -15135,7 +15105,7 @@
         <v>-1.918</v>
       </c>
       <c r="E51" t="n">
-        <v>1.04857700694283</v>
+        <v>1.40600722457742</v>
       </c>
     </row>
     <row r="52">
@@ -15152,7 +15122,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>1.56901119809271</v>
+        <v>1.17132821157781</v>
       </c>
     </row>
     <row r="53">
@@ -15169,7 +15139,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E53" t="n">
-        <v>1.1371033526549</v>
+        <v>1.17749651535779</v>
       </c>
     </row>
     <row r="54">
@@ -15186,7 +15156,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>5.36155911521455</v>
+        <v>4.49294799327635</v>
       </c>
     </row>
     <row r="55">
@@ -15203,7 +15173,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>1.6493620803524</v>
+        <v>1.82618056414388</v>
       </c>
     </row>
     <row r="56">
@@ -15220,7 +15190,7 @@
         <v>1.311</v>
       </c>
       <c r="E56" t="n">
-        <v>1.8157202676089</v>
+        <v>1.80540602676014</v>
       </c>
     </row>
     <row r="57">
@@ -15237,7 +15207,7 @@
         <v>2.862</v>
       </c>
       <c r="E57" t="n">
-        <v>1.74309474723544</v>
+        <v>1.82538062872544</v>
       </c>
     </row>
     <row r="58">
@@ -15458,7 +15428,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>45.3846153846154</v>
+        <v>50.4703679846882</v>
       </c>
     </row>
     <row r="71">
@@ -15738,10 +15708,10 @@
         <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.142857142857143</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="3">
@@ -15755,10 +15725,10 @@
         <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="4">
@@ -15814,92 +15784,92 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.357142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.357142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.357142857142857</v>
+        <v>0.928571428571429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.357142857142857</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.214285714285714</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
@@ -15908,38 +15878,38 @@
         <v>42</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.142857142857143</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -15950,7 +15920,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
@@ -15967,7 +15937,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
@@ -15984,13 +15954,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -16001,13 +15971,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
@@ -16018,13 +15988,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
@@ -16035,13 +16005,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -16052,13 +16022,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -16069,13 +16039,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -16086,341 +16056,18 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" t="n">
-        <v>14</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" t="n">
-        <v>13</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.928571428571429</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="n">
-        <v>13</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.928571428571429</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.857142857142857</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" t="n">
-        <v>12</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.857142857142857</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" t="n">
-        <v>11</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.785714285714286</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" t="n">
-        <v>8</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-      <c r="D34" t="n">
-        <v>6</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.428571428571429</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.357142857142857</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.214285714285714</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>19</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.142857142857143</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="s">
-        <v>67</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>
